--- a/base_datas/media_uf_detalhamento.xlsx
+++ b/base_datas/media_uf_detalhamento.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>populacao_24</t>
+          <t>populacao_25</t>
         </is>
       </c>
     </row>
@@ -603,115 +603,118 @@
         </is>
       </c>
       <c r="B2">
-        <v>283.9775242792232</v>
+        <v>894.9689191433796</v>
       </c>
       <c r="C2">
-        <v>58.47010637694278</v>
+        <v>58.20024431209693</v>
       </c>
       <c r="D2">
-        <v>4708.919366845685</v>
+        <v>5144.03302271441</v>
       </c>
       <c r="E2">
-        <v>148.931963826786</v>
+        <v>185.0769405388737</v>
       </c>
       <c r="F2">
-        <v>268.4665554996709</v>
+        <v>873.6929133176325</v>
       </c>
       <c r="G2">
-        <v>11.30044141402871</v>
+        <v>17.82620918628089</v>
       </c>
       <c r="H2">
-        <v>33.24050536334192</v>
+        <v>34.49796639466256</v>
       </c>
       <c r="I2">
-        <v>139.0290148303992</v>
+        <v>146.1711518736456</v>
       </c>
       <c r="J2">
-        <v>50.14279054147561</v>
+        <v>49.60194126070601</v>
       </c>
       <c r="K2">
-        <v>1.267677186271374</v>
+        <v>-9.57655712571925E-15</v>
       </c>
       <c r="L2">
-        <v>2480.237592097682</v>
+        <v>2816.609895948105</v>
       </c>
       <c r="M2">
-        <v>773.7784998295582</v>
+        <v>801.0906826104025</v>
       </c>
       <c r="N2">
-        <v>1454.903274918445</v>
+        <v>1526.332444155902</v>
       </c>
       <c r="O2">
-        <v>103.5796465647662</v>
+        <v>155.2478704412039</v>
       </c>
       <c r="P2">
-        <v>47.06429286243747</v>
+        <v>43.72352342891234</v>
       </c>
       <c r="S2">
-        <v>36.38769005012696</v>
+        <v>18.89818924044165</v>
       </c>
       <c r="T2">
-        <v>23.38592123790895</v>
+        <v>590.2526605040576</v>
       </c>
       <c r="U2">
-        <v>18.99895238496076</v>
+        <v>25.66244775348621</v>
       </c>
       <c r="V2">
-        <v>115.8702234361565</v>
+        <v>115.4932766648462</v>
       </c>
       <c r="W2">
-        <v>114.0085705838442</v>
+        <v>144.3648275101686</v>
       </c>
       <c r="Z2">
-        <v>0.04021396160001997</v>
+        <v>0.6942080863176217</v>
       </c>
       <c r="AA2">
-        <v>6.236968445975029</v>
+        <v>5.83325659217789</v>
       </c>
       <c r="AB2">
-        <v>6.323907518061684</v>
+        <v>13.32550288233666</v>
       </c>
       <c r="AC2">
-        <v>-1.574424552332985E-16</v>
+        <v>4.558890560611722E-16</v>
       </c>
       <c r="AF2">
-        <v>33.24050536334192</v>
+        <v>34.49796639466256</v>
       </c>
       <c r="AH2">
-        <v>1208.125410742412</v>
+        <v>1327.005041802211</v>
       </c>
       <c r="AJ2">
-        <v>21.90896699659194</v>
+        <v>22.93279057850083</v>
       </c>
       <c r="AK2">
-        <v>597.6844139547926</v>
+        <v>727.6540774868911</v>
       </c>
       <c r="AL2">
-        <v>139.1760697288774</v>
+        <v>168.4318370655073</v>
       </c>
       <c r="AM2">
-        <v>212.172614046971</v>
+        <v>276.5520292989233</v>
       </c>
       <c r="AN2">
-        <v>71.77424245691923</v>
+        <v>44.89368097454487</v>
       </c>
       <c r="AO2">
-        <v>229.3958741711184</v>
+        <v>249.140438741527</v>
       </c>
       <c r="AP2">
-        <v>673.6836532459413</v>
+        <v>673.4834610190576</v>
       </c>
       <c r="AQ2">
-        <v>44.30078901528957</v>
+        <v>50.4139133873451</v>
       </c>
       <c r="AR2">
-        <v>2.653467417885448</v>
+        <v>2.465137606402835</v>
       </c>
       <c r="AS2">
-        <v>5.497127042208</v>
+        <v>5.722056927254454</v>
+      </c>
+      <c r="AT2">
+        <v>0.04486931973408614</v>
       </c>
       <c r="AU2">
-        <v>52.04823447420299</v>
+        <v>71.99264517145608</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -724,121 +727,124 @@
         </is>
       </c>
       <c r="B3">
-        <v>384.7464596481314</v>
+        <v>469.9736510163895</v>
       </c>
       <c r="C3">
-        <v>250.5254867752025</v>
+        <v>252.2333172396661</v>
       </c>
       <c r="D3">
-        <v>7755.219101057429</v>
+        <v>8497.794316361009</v>
       </c>
       <c r="E3">
-        <v>504.3930853758276</v>
+        <v>308.5114343023655</v>
       </c>
       <c r="F3">
-        <v>361.3245782872646</v>
+        <v>441.389286924589</v>
       </c>
       <c r="G3">
-        <v>19.59409941056397</v>
+        <v>25.03755974220178</v>
       </c>
       <c r="H3">
-        <v>50.0797981152726</v>
+        <v>57.34552562709868</v>
       </c>
       <c r="I3">
-        <v>203.9686447493451</v>
+        <v>201.6556388832431</v>
       </c>
       <c r="J3">
-        <v>102.1689299796294</v>
+        <v>108.7685701670524</v>
       </c>
       <c r="K3">
-        <v>4.607981602868602</v>
+        <v>2.225093273152927E-15</v>
       </c>
       <c r="L3">
-        <v>5023.005011956842</v>
+        <v>5603.510163220668</v>
       </c>
       <c r="M3">
-        <v>1175.148902203338</v>
+        <v>1282.273452523542</v>
       </c>
       <c r="N3">
-        <v>1557.065186897248</v>
+        <v>1612.0107006168</v>
       </c>
       <c r="O3">
-        <v>411.8137206445739</v>
+        <v>241.2324670155197</v>
       </c>
       <c r="P3">
-        <v>53.45761813599454</v>
+        <v>70.20745227887586</v>
       </c>
       <c r="S3">
-        <v>77.64070576235366</v>
+        <v>48.96397973583473</v>
       </c>
       <c r="T3">
-        <v>44.55259009968495</v>
+        <v>49.81418581980702</v>
       </c>
       <c r="U3">
-        <v>20.74595367361743</v>
+        <v>27.26686643469086</v>
       </c>
       <c r="V3">
-        <v>162.6604540520764</v>
+        <v>177.6335143171896</v>
       </c>
       <c r="W3">
-        <v>131.9930735744991</v>
+        <v>179.8888200041839</v>
       </c>
       <c r="Z3">
-        <v>9.726609499281953</v>
+        <v>14.07320582535628</v>
       </c>
       <c r="AA3">
-        <v>14.69194982362485</v>
+        <v>20.31243502068962</v>
       </c>
       <c r="AB3">
-        <v>9.621127085044288</v>
+        <v>9.223219405119215</v>
       </c>
       <c r="AC3">
-        <v>-4.731484615502731E-17</v>
+        <v>-1.756299833917468E-15</v>
+      </c>
+      <c r="AE3">
+        <v>69.36389114743217</v>
       </c>
       <c r="AF3">
-        <v>74.30122841588788</v>
+        <v>106.0644104000054</v>
       </c>
       <c r="AG3">
-        <v>13.74765266434969</v>
+        <v>3.465389260560617</v>
       </c>
       <c r="AH3">
-        <v>2410.756977556513</v>
+        <v>2701.325272469679</v>
       </c>
       <c r="AJ3">
-        <v>308.2884427296185</v>
+        <v>304.9776563580851</v>
       </c>
       <c r="AK3">
-        <v>887.312121941715</v>
+        <v>946.6766644709629</v>
       </c>
       <c r="AL3">
-        <v>213.4716504983761</v>
+        <v>200.826149297343</v>
       </c>
       <c r="AM3">
-        <v>877.2927389533542</v>
+        <v>1193.743020249705</v>
       </c>
       <c r="AN3">
-        <v>43.75560256152875</v>
+        <v>45.26075649540669</v>
       </c>
       <c r="AO3">
-        <v>282.1274777157376</v>
+        <v>217.330592930749</v>
       </c>
       <c r="AP3">
-        <v>957.3073891185572</v>
+        <v>1025.554099271947</v>
       </c>
       <c r="AQ3">
-        <v>55.66770053195975</v>
+        <v>63.3634633795448</v>
       </c>
       <c r="AR3">
-        <v>81.26435008502601</v>
+        <v>123.0385056335996</v>
       </c>
       <c r="AS3">
-        <v>7.608298175301051</v>
+        <v>8.273678364287726</v>
       </c>
       <c r="AT3">
-        <v>12.04664364024802</v>
+        <v>7.020164462480571</v>
       </c>
       <c r="AU3">
-        <v>79.73287687264315</v>
+        <v>98.8830627450921</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -851,127 +857,118 @@
         </is>
       </c>
       <c r="B4">
-        <v>262.3330836316928</v>
+        <v>325.3678698994866</v>
       </c>
       <c r="C4">
-        <v>64.06975969110154</v>
+        <v>75.61869896649102</v>
       </c>
       <c r="D4">
-        <v>5801.495897490706</v>
+        <v>6637.358642699217</v>
       </c>
       <c r="E4">
-        <v>93.35467677090958</v>
+        <v>155.5826709797691</v>
       </c>
       <c r="F4">
-        <v>247.3356756352726</v>
+        <v>310.7953895925899</v>
       </c>
       <c r="G4">
-        <v>9.329441654090658</v>
+        <v>9.812272409960814</v>
       </c>
       <c r="H4">
-        <v>23.71263988666897</v>
+        <v>25.74414122045831</v>
       </c>
       <c r="I4">
-        <v>93.25413918778608</v>
+        <v>102.5788150417113</v>
       </c>
       <c r="J4">
-        <v>22.34011478688965</v>
+        <v>26.47399147638443</v>
       </c>
       <c r="K4">
-        <v>7.684498783777746</v>
+        <v>4.201251580589412</v>
       </c>
       <c r="L4">
-        <v>3737.022178464857</v>
+        <v>4311.834674195403</v>
       </c>
       <c r="M4">
-        <v>1024.277981300703</v>
+        <v>1166.483104984306</v>
       </c>
       <c r="N4">
-        <v>1040.195737725146</v>
+        <v>1159.040863519508</v>
       </c>
       <c r="O4">
-        <v>70.35762422720502</v>
+        <v>106.3890754254116</v>
       </c>
       <c r="P4">
-        <v>22.21340262371529</v>
-      </c>
-      <c r="Q4">
-        <v>0.001101146161570692</v>
+        <v>30.03705895881413</v>
       </c>
       <c r="S4">
-        <v>12.44941111232888</v>
+        <v>34.675683724264</v>
       </c>
       <c r="T4">
-        <v>7.959743094377467</v>
+        <v>9.078172025331476</v>
       </c>
       <c r="U4">
-        <v>4.017368049207844</v>
+        <v>5.211779553699727</v>
       </c>
       <c r="V4">
-        <v>108.2189742561933</v>
+        <v>122.096232831587</v>
       </c>
       <c r="W4">
-        <v>98.51332189038784</v>
+        <v>121.1094223004467</v>
       </c>
       <c r="Z4">
-        <v>53.16114547734889</v>
+        <v>89.96756525511151</v>
       </c>
       <c r="AA4">
-        <v>6.851357245963422</v>
+        <v>7.875816139159996</v>
       </c>
       <c r="AB4">
-        <v>4.627276059213437</v>
+        <v>3.466088213127423</v>
       </c>
       <c r="AC4">
-        <v>3.423056916593845E-16</v>
-      </c>
-      <c r="AE4">
-        <v>0.1920357684463735</v>
+        <v>-6.387367487528611E-16</v>
       </c>
       <c r="AF4">
-        <v>22.17310405562237</v>
-      </c>
-      <c r="AG4">
-        <v>46.61364158392152</v>
+        <v>25.74414122045831</v>
       </c>
       <c r="AH4">
-        <v>1440.917720980991</v>
+        <v>1612.485555776813</v>
       </c>
       <c r="AJ4">
-        <v>128.0616838114944</v>
+        <v>116.426879052568</v>
       </c>
       <c r="AK4">
-        <v>979.3497619924641</v>
+        <v>1283.056255230075</v>
       </c>
       <c r="AL4">
-        <v>166.6417162107782</v>
+        <v>176.0717972052217</v>
       </c>
       <c r="AM4">
-        <v>869.6201411579186</v>
+        <v>1048.465175036825</v>
       </c>
       <c r="AN4">
-        <v>59.31429165306485</v>
+        <v>31.15699389975155</v>
       </c>
       <c r="AO4">
-        <v>93.11686265814495</v>
+        <v>44.17201799414918</v>
       </c>
       <c r="AP4">
-        <v>855.044916483629</v>
+        <v>933.1158018555973</v>
       </c>
       <c r="AQ4">
-        <v>16.98220833631826</v>
+        <v>18.80508433381266</v>
       </c>
       <c r="AR4">
-        <v>96.97849385210641</v>
+        <v>180.4638893303195</v>
       </c>
       <c r="AS4">
-        <v>38.81194067963058</v>
+        <v>39.43115457723623</v>
       </c>
       <c r="AT4">
-        <v>7.790905945570604</v>
+        <v>9.216481623146493</v>
       </c>
       <c r="AU4">
-        <v>75.63153317108085</v>
+        <v>62.18067528970458</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -984,121 +981,118 @@
         </is>
       </c>
       <c r="B5">
-        <v>432.4923272178929</v>
+        <v>380.0789903829339</v>
       </c>
       <c r="C5">
-        <v>43.07636459446329</v>
+        <v>95.2729091053548</v>
       </c>
       <c r="D5">
-        <v>5564.364124088297</v>
+        <v>6826.507196228828</v>
       </c>
       <c r="E5">
-        <v>188.8378211756846</v>
+        <v>278.1818707328283</v>
       </c>
       <c r="F5">
-        <v>409.678003191471</v>
+        <v>353.4808423584493</v>
       </c>
       <c r="G5">
-        <v>15.7303846223186</v>
+        <v>19.32795782244716</v>
       </c>
       <c r="H5">
-        <v>18.66227441458334</v>
+        <v>18.97340507482217</v>
       </c>
       <c r="I5">
-        <v>48.03545249752564</v>
+        <v>104.6739667449986</v>
       </c>
       <c r="J5">
-        <v>24.58500314375689</v>
+        <v>38.23539691303361</v>
       </c>
       <c r="K5">
-        <v>7.646326556777328E-15</v>
+        <v>-1.913493609694627E-14</v>
       </c>
       <c r="L5">
-        <v>2808.334043554235</v>
+        <v>3657.282603244038</v>
       </c>
       <c r="M5">
-        <v>1281.416023555453</v>
+        <v>1589.830202482057</v>
       </c>
       <c r="N5">
-        <v>1474.614056978609</v>
+        <v>1579.394390502732</v>
       </c>
       <c r="O5">
-        <v>170.5884994550707</v>
+        <v>244.4268370315762</v>
       </c>
       <c r="P5">
-        <v>7.948240073520872</v>
+        <v>19.3318941806601</v>
       </c>
       <c r="S5">
-        <v>17.11385885296807</v>
+        <v>32.26796491812448</v>
       </c>
       <c r="T5">
-        <v>7.85427021982588</v>
+        <v>8.360243086266131</v>
       </c>
       <c r="U5">
-        <v>3.415722244136659</v>
+        <v>4.331305241040625</v>
       </c>
       <c r="V5">
-        <v>268.8023174743369</v>
+        <v>209.2408152723003</v>
       </c>
       <c r="W5">
-        <v>143.9099744510934</v>
+        <v>135.4768295823071</v>
       </c>
       <c r="Z5">
-        <v>8.733327731629506E-15</v>
+        <v>-3.507515107695887E-14</v>
       </c>
       <c r="AA5">
-        <v>10.84871691227943</v>
+        <v>12.67583155862383</v>
       </c>
       <c r="AB5">
-        <v>17.35718235818737</v>
+        <v>15.41689112075062</v>
       </c>
       <c r="AC5">
-        <v>1.909637509053752E-15</v>
+        <v>7.488114242259562E-16</v>
       </c>
       <c r="AE5">
-        <v>1.351484528409652</v>
+        <v>1.127458624884201</v>
       </c>
       <c r="AF5">
-        <v>21.32215864087735</v>
-      </c>
-      <c r="AG5">
-        <v>4.816122862275973E-15</v>
+        <v>22.31710263983292</v>
       </c>
       <c r="AH5">
-        <v>1265.787771688369</v>
+        <v>1475.753466498959</v>
       </c>
       <c r="AJ5">
-        <v>243.6982539573841</v>
+        <v>207.3128435946604</v>
       </c>
       <c r="AK5">
-        <v>766.0195711402215</v>
+        <v>1081.142982164425</v>
       </c>
       <c r="AL5">
-        <v>102.0030572917601</v>
+        <v>122.6606480148862</v>
       </c>
       <c r="AM5">
-        <v>110.8639281036647</v>
+        <v>151.0833601573153</v>
       </c>
       <c r="AN5">
-        <v>53.66015491297819</v>
+        <v>43.93923592692951</v>
       </c>
       <c r="AO5">
-        <v>329.6521225190934</v>
+        <v>610.255457692397</v>
       </c>
       <c r="AP5">
-        <v>1048.430349903783</v>
+        <v>1193.512142938834</v>
       </c>
       <c r="AQ5">
-        <v>23.06811841105495</v>
+        <v>25.15409138315029</v>
       </c>
       <c r="AR5">
-        <v>52.23136820315543</v>
+        <v>70.83186259035901</v>
       </c>
       <c r="AS5">
-        <v>30.7856204179652</v>
+        <v>31.70429246990802</v>
       </c>
       <c r="AU5">
-        <v>233.6363461500194</v>
+        <v>278.9540013713575</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1111,133 +1105,127 @@
         </is>
       </c>
       <c r="B6">
-        <v>433.6794197448787</v>
+        <v>479.9951160588133</v>
       </c>
       <c r="C6">
-        <v>75.86444452453412</v>
+        <v>61.66303521375799</v>
       </c>
       <c r="D6">
-        <v>5598.413845018443</v>
+        <v>6223.911268288663</v>
       </c>
       <c r="E6">
-        <v>132.5410674461402</v>
+        <v>158.4407086671033</v>
       </c>
       <c r="F6">
-        <v>398.0888919558578</v>
+        <v>441.7099515348201</v>
       </c>
       <c r="G6">
-        <v>34.20047579230813</v>
+        <v>36.98476428930296</v>
       </c>
       <c r="H6">
-        <v>21.82446593253701</v>
+        <v>18.35858256263318</v>
       </c>
       <c r="I6">
-        <v>201.7613211052404</v>
+        <v>206.7525909387922</v>
       </c>
       <c r="J6">
-        <v>51.25410768424558</v>
+        <v>36.60554045029787</v>
       </c>
       <c r="K6">
-        <v>0.04072115496403581</v>
+        <v>0.6996129452472266</v>
       </c>
       <c r="L6">
-        <v>3806.355058723455</v>
+        <v>4267.270060294652</v>
       </c>
       <c r="M6">
-        <v>776.1079829920337</v>
+        <v>842.4739198656512</v>
       </c>
       <c r="N6">
-        <v>1015.950803302954</v>
+        <v>1114.167288128358</v>
       </c>
       <c r="O6">
-        <v>61.96621050364661</v>
+        <v>94.2367340321332</v>
       </c>
       <c r="P6">
-        <v>50.98482924496813</v>
+        <v>55.57066003351745</v>
       </c>
       <c r="Q6">
-        <v>4.408949130575656</v>
-      </c>
-      <c r="R6">
-        <v>0.2392146017699115</v>
+        <v>2.890179627836936</v>
       </c>
       <c r="S6">
-        <v>47.49591997639745</v>
+        <v>40.82733965845946</v>
       </c>
       <c r="T6">
-        <v>34.25032783646806</v>
+        <v>37.05558044181533</v>
       </c>
       <c r="U6">
-        <v>22.31160209988444</v>
+        <v>31.14687603563921</v>
       </c>
       <c r="V6">
-        <v>186.4353351411869</v>
+        <v>194.1335105238184</v>
       </c>
       <c r="W6">
-        <v>155.3179352543457</v>
+        <v>179.5814449298117</v>
       </c>
       <c r="Z6">
-        <v>6.911164432982932</v>
+        <v>2.503829583818792</v>
       </c>
       <c r="AA6">
-        <v>26.51393812760719</v>
+        <v>29.82321939936547</v>
       </c>
       <c r="AB6">
-        <v>11.17015336476996</v>
+        <v>10.22420829723585</v>
       </c>
       <c r="AC6">
-        <v>3.794645696670106E-16</v>
+        <v>-3.258733423216428E-16</v>
       </c>
       <c r="AD6">
-        <v>13.77368738286023</v>
-      </c>
-      <c r="AE6">
-        <v>0.4695450910594603</v>
+        <v>2.635221099284987</v>
       </c>
       <c r="AF6">
-        <v>26.67364865582171</v>
+        <v>23.62151301837771</v>
       </c>
       <c r="AG6">
-        <v>0.4359254260015787</v>
+        <v>4.621117106024005</v>
       </c>
       <c r="AH6">
-        <v>2020.033599755949</v>
+        <v>2242.514881929888</v>
       </c>
       <c r="AJ6">
-        <v>116.8262065276472</v>
+        <v>144.9631577614369</v>
       </c>
       <c r="AK6">
-        <v>628.1094877084598</v>
+        <v>673.7177190173793</v>
       </c>
       <c r="AL6">
-        <v>151.3757754761841</v>
+        <v>153.4777547723496</v>
       </c>
       <c r="AM6">
-        <v>726.1446511484451</v>
+        <v>929.2190268587008</v>
       </c>
       <c r="AN6">
-        <v>33.80545496532017</v>
+        <v>37.64761198677994</v>
       </c>
       <c r="AO6">
-        <v>135.2930619656342</v>
+        <v>86.53082221630774</v>
       </c>
       <c r="AP6">
-        <v>642.4178882572597</v>
+        <v>697.7292282670109</v>
       </c>
       <c r="AQ6">
-        <v>44.53188941506127</v>
+        <v>49.49618097168229</v>
       </c>
       <c r="AR6">
-        <v>27.39004030159203</v>
+        <v>36.77206252885046</v>
       </c>
       <c r="AS6">
-        <v>11.11107623480018</v>
+        <v>11.74390335340019</v>
       </c>
       <c r="AT6">
-        <v>27.91262026169598</v>
+        <v>18.91179797528065</v>
       </c>
       <c r="AU6">
-        <v>53.54609717333355</v>
+        <v>51.01705219217269</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1250,124 +1238,121 @@
         </is>
       </c>
       <c r="B7">
-        <v>329.8366517521965</v>
+        <v>384.4811157015105</v>
       </c>
       <c r="C7">
-        <v>113.8862578850042</v>
+        <v>121.3274378029106</v>
       </c>
       <c r="D7">
-        <v>5472.115599049771</v>
+        <v>6139.231718370922</v>
       </c>
       <c r="E7">
-        <v>180.5844216836915</v>
+        <v>256.7116963755445</v>
       </c>
       <c r="F7">
-        <v>311.3076461838026</v>
+        <v>365.8091645053125</v>
       </c>
       <c r="G7">
-        <v>16.89063552911468</v>
+        <v>17.63154888209652</v>
       </c>
       <c r="H7">
-        <v>33.1314830165348</v>
+        <v>27.14763027121637</v>
       </c>
       <c r="I7">
-        <v>179.8323650150715</v>
+        <v>188.7573278599359</v>
       </c>
       <c r="J7">
-        <v>50.40153269182081</v>
+        <v>55.79521615261831</v>
       </c>
       <c r="K7">
-        <v>6.139347699230448E-16</v>
+        <v>-5.778243768243983E-18</v>
       </c>
       <c r="L7">
-        <v>3676.808738270188</v>
+        <v>4220.498075212953</v>
       </c>
       <c r="M7">
-        <v>862.803712774415</v>
+        <v>925.9579679664495</v>
       </c>
       <c r="N7">
-        <v>932.503148005168</v>
+        <v>992.7756751915193</v>
       </c>
       <c r="O7">
-        <v>92.83133703131942</v>
+        <v>149.2937017078393</v>
       </c>
       <c r="P7">
-        <v>52.76489997959168</v>
+        <v>56.33570512634405</v>
       </c>
       <c r="S7">
-        <v>62.53030279399584</v>
+        <v>80.168659035941</v>
       </c>
       <c r="T7">
-        <v>27.74546308218397</v>
+        <v>33.85298362441344</v>
       </c>
       <c r="U7">
-        <v>13.3345603795989</v>
+        <v>15.43298898813537</v>
       </c>
       <c r="V7">
-        <v>129.5503966403055</v>
+        <v>146.9369335779951</v>
       </c>
       <c r="W7">
-        <v>141.122740942157</v>
+        <v>170.4074171296322</v>
       </c>
       <c r="Z7">
-        <v>-2.799074128059491E-15</v>
+        <v>1.33459498137387</v>
       </c>
       <c r="AA7">
-        <v>13.81978378274976</v>
+        <v>14.56599936909887</v>
       </c>
       <c r="AB7">
-        <v>5.004835910821862</v>
+        <v>4.348428789567165</v>
       </c>
       <c r="AC7">
-        <v>4.579769535072647E-16</v>
-      </c>
-      <c r="AE7">
-        <v>50.83445850914205</v>
+        <v>4.712102618128926E-16</v>
       </c>
       <c r="AF7">
-        <v>37.72602609458081</v>
+        <v>48.73814505986701</v>
       </c>
       <c r="AG7">
-        <v>19.57291938892237</v>
+        <v>0.1594867854030781</v>
       </c>
       <c r="AH7">
-        <v>1806.86334115825</v>
+        <v>2014.387546182184</v>
       </c>
       <c r="AJ7">
-        <v>43.01834268061579</v>
+        <v>46.47373796240884</v>
       </c>
       <c r="AK7">
-        <v>713.8915837024755</v>
+        <v>754.0835256725609</v>
       </c>
       <c r="AL7">
-        <v>155.4650121843194</v>
+        <v>166.4126231966147</v>
       </c>
       <c r="AM7">
-        <v>842.1532054943482</v>
+        <v>1138.510859087723</v>
       </c>
       <c r="AN7">
-        <v>38.88291868695414</v>
+        <v>37.65938697484417</v>
       </c>
       <c r="AO7">
-        <v>81.61155670861973</v>
+        <v>63.37973729938796</v>
       </c>
       <c r="AP7">
-        <v>698.4358514127954</v>
+        <v>751.4022631049529</v>
       </c>
       <c r="AQ7">
-        <v>59.21116480170816</v>
+        <v>67.11187696858501</v>
       </c>
       <c r="AR7">
-        <v>58.56215226603925</v>
+        <v>72.04290975011938</v>
       </c>
       <c r="AS7">
-        <v>3.292123039337649</v>
+        <v>4.997587230011527</v>
       </c>
       <c r="AT7">
-        <v>0.3846338740865817</v>
+        <v>0.3220572710934896</v>
       </c>
       <c r="AU7">
-        <v>86.99350655930792</v>
+        <v>86.43201534027911</v>
       </c>
       <c r="AV7">
         <v>1</v>
@@ -1380,109 +1365,109 @@
         </is>
       </c>
       <c r="B8">
-        <v>8328.623806946987</v>
+        <v>9021.561814742507</v>
       </c>
       <c r="C8">
-        <v>922.5491187963864</v>
+        <v>1003.371916347531</v>
       </c>
       <c r="D8">
-        <v>2372.308437906705</v>
+        <v>2362.819582725343</v>
       </c>
       <c r="E8">
-        <v>1442.628285151825</v>
+        <v>1695.772933258678</v>
       </c>
       <c r="F8">
-        <v>8141.057707744824</v>
+        <v>8818.093409888021</v>
       </c>
       <c r="G8">
-        <v>187.5660992021639</v>
+        <v>203.4684048544846</v>
       </c>
       <c r="I8">
-        <v>813.1475211762837</v>
+        <v>890.0134890431743</v>
       </c>
       <c r="J8">
-        <v>108.1222277926444</v>
+        <v>111.897395864859</v>
       </c>
       <c r="K8">
-        <v>1.279369827458352</v>
+        <v>1.46103143949791</v>
       </c>
       <c r="L8">
-        <v>1288.466423449235</v>
+        <v>1212.741071534276</v>
       </c>
       <c r="M8">
-        <v>18.79229684144322</v>
+        <v>17.18444441737943</v>
       </c>
       <c r="N8">
-        <v>1065.049717616026</v>
+        <v>1132.894066773688</v>
       </c>
       <c r="O8">
-        <v>532.1228890331223</v>
+        <v>662.5337091473554</v>
       </c>
       <c r="P8">
-        <v>459.8563450099872</v>
+        <v>603.0005718077252</v>
       </c>
       <c r="Q8">
-        <v>0.004455518238122473</v>
+        <v>0.00117491113314129</v>
       </c>
       <c r="R8">
-        <v>1.140091316332408</v>
+        <v>1.359412456008694</v>
       </c>
       <c r="S8">
-        <v>449.5045042741453</v>
+        <v>428.8780649364567</v>
       </c>
       <c r="T8">
-        <v>447.6080372285537</v>
+        <v>457.5150913560984</v>
       </c>
       <c r="U8">
-        <v>208.2172361974482</v>
+        <v>159.9617542132718</v>
       </c>
       <c r="V8">
-        <v>1164.212709481437</v>
+        <v>1288.927598841336</v>
       </c>
       <c r="W8">
-        <v>1653.10405043821</v>
+        <v>1886.389658119943</v>
       </c>
       <c r="X8">
-        <v>3928.699041553994</v>
+        <v>4203.961932344067</v>
       </c>
       <c r="Y8">
-        <v>619.6702869300105</v>
+        <v>660.8749918098674</v>
       </c>
       <c r="Z8">
-        <v>119.546345915171</v>
+        <v>160.4623832034374</v>
       </c>
       <c r="AA8">
-        <v>97.61441588122374</v>
+        <v>112.316207423073</v>
       </c>
       <c r="AB8">
-        <v>89.95168332094012</v>
+        <v>91.15219743141159</v>
       </c>
       <c r="AH8">
-        <v>162.7477208364708</v>
+        <v>138.853704719445</v>
       </c>
       <c r="AI8">
-        <v>429.4473048975834</v>
+        <v>467.5037520550409</v>
       </c>
       <c r="AJ8">
-        <v>6.100514684435994</v>
+        <v>4.808966761976296</v>
       </c>
       <c r="AK8">
-        <v>363.3375090669293</v>
+        <v>419.135125568129</v>
       </c>
       <c r="AL8">
-        <v>134.2162605294725</v>
+        <v>96.11884881672688</v>
       </c>
       <c r="AM8">
-        <v>25.43321615666796</v>
+        <v>8.40881313984889</v>
       </c>
       <c r="AN8">
-        <v>12.19455021727776</v>
+        <v>6.995374812431117</v>
       </c>
       <c r="AO8">
-        <v>154.9893470603973</v>
+        <v>70.91648566067794</v>
       </c>
       <c r="AU8">
-        <v>18.79229684144322</v>
+        <v>17.18444441737943</v>
       </c>
       <c r="AV8">
         <v>1</v>
@@ -1495,133 +1480,130 @@
         </is>
       </c>
       <c r="B9">
-        <v>714.362047180294</v>
+        <v>790.6582087129118</v>
       </c>
       <c r="C9">
-        <v>148.7690381947118</v>
+        <v>158.5523726487649</v>
       </c>
       <c r="D9">
-        <v>5969.072152068725</v>
+        <v>6679.391789555311</v>
       </c>
       <c r="E9">
-        <v>477.5388389826576</v>
+        <v>535.0463308624343</v>
       </c>
       <c r="F9">
-        <v>652.8652102145556</v>
+        <v>718.9726079061346</v>
       </c>
       <c r="G9">
-        <v>59.07915921537537</v>
+        <v>69.5204831630213</v>
       </c>
       <c r="H9">
-        <v>20.95320716981174</v>
+        <v>23.81629408131529</v>
       </c>
       <c r="I9">
-        <v>124.2498779661829</v>
+        <v>138.0646013358665</v>
       </c>
       <c r="J9">
-        <v>88.27896602696489</v>
+        <v>92.28136400754896</v>
       </c>
       <c r="K9">
-        <v>5.637898597290782E-15</v>
+        <v>1.51147829263056E-15</v>
       </c>
       <c r="L9">
-        <v>2975.990867038965</v>
+        <v>3304.469166646214</v>
       </c>
       <c r="M9">
-        <v>1966.612409953554</v>
+        <v>2230.641139396661</v>
       </c>
       <c r="N9">
-        <v>1026.468875076205</v>
+        <v>1144.281483512436</v>
       </c>
       <c r="O9">
-        <v>335.5287259875339</v>
+        <v>399.8448725706032</v>
       </c>
       <c r="P9">
-        <v>129.5155739543233</v>
+        <v>139.2252343043226</v>
       </c>
       <c r="Q9">
-        <v>0.4113173667996252</v>
-      </c>
-      <c r="R9">
-        <v>1.061057371096587</v>
+        <v>0.769951680159711</v>
       </c>
       <c r="S9">
-        <v>65.60498358482162</v>
+        <v>55.62418280156471</v>
       </c>
       <c r="T9">
-        <v>73.67848805795653</v>
+        <v>84.04584480010773</v>
       </c>
       <c r="U9">
-        <v>55.40570566341051</v>
+        <v>60.56915600022906</v>
       </c>
       <c r="V9">
-        <v>358.0321030652809</v>
+        <v>389.3947761583281</v>
       </c>
       <c r="W9">
-        <v>165.7489134279078</v>
+        <v>184.9628309474697</v>
       </c>
       <c r="Z9">
-        <v>-2.33367484043479E-14</v>
+        <v>-6.34268656961232E-15</v>
       </c>
       <c r="AA9">
-        <v>22.71500072978396</v>
+        <v>24.07295335440537</v>
       </c>
       <c r="AB9">
-        <v>36.3641584855914</v>
+        <v>45.44752980861593</v>
       </c>
       <c r="AC9">
-        <v>7.796259474913251E-16</v>
+        <v>-6.278861419867685E-16</v>
       </c>
       <c r="AD9">
-        <v>0.0005174751895457067</v>
+        <v>7.30219373921617E-05</v>
       </c>
       <c r="AE9">
-        <v>7.775627508696815</v>
+        <v>1.302203162690968</v>
       </c>
       <c r="AF9">
-        <v>30.12631712420815</v>
+        <v>32.92668132159382</v>
       </c>
       <c r="AG9">
-        <v>0.04481679917041134</v>
+        <v>0.7783757766095443</v>
       </c>
       <c r="AH9">
-        <v>1680.309849608721</v>
+        <v>1871.305378133717</v>
       </c>
       <c r="AJ9">
-        <v>521.4890362154434</v>
+        <v>493.2086469041249</v>
       </c>
       <c r="AK9">
-        <v>502.9793298405478</v>
+        <v>594.2088750105023</v>
       </c>
       <c r="AL9">
-        <v>105.5100041113984</v>
+        <v>112.5080505617925</v>
       </c>
       <c r="AM9">
-        <v>119.6088866513578</v>
+        <v>150.4654640226338</v>
       </c>
       <c r="AN9">
-        <v>26.15031267009956</v>
+        <v>24.64645468572035</v>
       </c>
       <c r="AO9">
-        <v>51.83488188982471</v>
+        <v>60.720561917257</v>
       </c>
       <c r="AP9">
-        <v>1471.991697285715</v>
+        <v>1661.612062229777</v>
       </c>
       <c r="AQ9">
-        <v>139.2809443092319</v>
+        <v>164.3934601199574</v>
       </c>
       <c r="AR9">
-        <v>46.8083627963502</v>
+        <v>78.51936957770826</v>
       </c>
       <c r="AS9">
-        <v>35.20171995212758</v>
+        <v>42.52857461990821</v>
       </c>
       <c r="AT9">
-        <v>34.29572368364749</v>
+        <v>30.34252179816709</v>
       </c>
       <c r="AU9">
-        <v>253.8144955494883</v>
+        <v>273.2803898727461</v>
       </c>
       <c r="AV9">
         <v>1</v>
@@ -1634,133 +1616,133 @@
         </is>
       </c>
       <c r="B10">
-        <v>801.1808960900592</v>
+        <v>1049.144448435148</v>
       </c>
       <c r="C10">
-        <v>401.4463945425169</v>
+        <v>409.7967542722584</v>
       </c>
       <c r="D10">
-        <v>7445.487162690816</v>
+        <v>8625.410919898761</v>
       </c>
       <c r="E10">
-        <v>591.3869995224143</v>
+        <v>430.9408922170603</v>
       </c>
       <c r="F10">
-        <v>744.5351836185223</v>
+        <v>986.0954855359961</v>
       </c>
       <c r="G10">
-        <v>54.762022109846</v>
+        <v>59.42296622465666</v>
       </c>
       <c r="H10">
-        <v>46.62151234989472</v>
+        <v>55.94800459214945</v>
       </c>
       <c r="I10">
-        <v>439.0215387698249</v>
+        <v>448.0284494320294</v>
       </c>
       <c r="J10">
-        <v>60.73673671275763</v>
+        <v>63.75106344565983</v>
       </c>
       <c r="K10">
-        <v>2.771440216094806</v>
+        <v>0.003813616686092018</v>
       </c>
       <c r="L10">
-        <v>4410.463635575903</v>
+        <v>5046.435505602432</v>
       </c>
       <c r="M10">
-        <v>2172.813246993797</v>
+        <v>2702.475648483372</v>
       </c>
       <c r="N10">
-        <v>862.2102801211154</v>
+        <v>876.4997658129571</v>
       </c>
       <c r="O10">
-        <v>187.6838021358213</v>
+        <v>293.7427468363926</v>
       </c>
       <c r="P10">
-        <v>655.7624787143446</v>
+        <v>128.297009046822</v>
       </c>
       <c r="Q10">
-        <v>2.457108623870302</v>
+        <v>0.5153444551148371</v>
       </c>
       <c r="R10">
-        <v>186.3840153070749</v>
+        <v>203.0695822454308</v>
       </c>
       <c r="S10">
-        <v>88.11049305497654</v>
+        <v>90.08850434898284</v>
       </c>
       <c r="T10">
-        <v>3.952602901418744</v>
+        <v>102.5978702832541</v>
       </c>
       <c r="U10">
-        <v>210.1385095529448</v>
+        <v>221.208280669138</v>
       </c>
       <c r="V10">
-        <v>328.1986546014265</v>
+        <v>427.7800852626311</v>
       </c>
       <c r="W10">
-        <v>206.3957662251058</v>
+        <v>239.6151266635368</v>
       </c>
       <c r="Z10">
-        <v>1.462825215322066</v>
+        <v>1.755153244749021</v>
       </c>
       <c r="AA10">
-        <v>33.93323268596276</v>
+        <v>36.36790491329101</v>
       </c>
       <c r="AB10">
-        <v>31.12076930138119</v>
+        <v>34.2797098299915</v>
       </c>
       <c r="AC10">
-        <v>1.329420482623623E-15</v>
+        <v>-2.019169747409806E-15</v>
       </c>
       <c r="AD10">
-        <v>4.335013754351508</v>
+        <v>40.04352829734064</v>
       </c>
       <c r="AE10">
-        <v>100.7207839866531</v>
+        <v>114.3676557073837</v>
       </c>
       <c r="AF10">
-        <v>27.21935860078375</v>
+        <v>27.08442199590593</v>
       </c>
       <c r="AG10">
-        <v>60.11727957839808</v>
+        <v>53.78938066054137</v>
       </c>
       <c r="AH10">
-        <v>3254.352640355078</v>
+        <v>3639.300559762842</v>
       </c>
       <c r="AJ10">
-        <v>231.2021784537687</v>
+        <v>220.3444655827873</v>
       </c>
       <c r="AK10">
-        <v>557.8444743448504</v>
+        <v>616.1131164216083</v>
       </c>
       <c r="AL10">
-        <v>97.28655957270369</v>
+        <v>99.16416880845948</v>
       </c>
       <c r="AM10">
-        <v>37.01800796903481</v>
+        <v>50.06964533972609</v>
       </c>
       <c r="AN10">
-        <v>54.90854701526122</v>
+        <v>49.65948560744007</v>
       </c>
       <c r="AO10">
-        <v>434.2275499011491</v>
+        <v>384.7022085587836</v>
       </c>
       <c r="AP10">
-        <v>1892.907606447631</v>
+        <v>2161.514190638619</v>
       </c>
       <c r="AQ10">
-        <v>165.6552512353593</v>
+        <v>173.986197156752</v>
       </c>
       <c r="AR10">
-        <v>67.53291364068636</v>
+        <v>81.93170741334393</v>
       </c>
       <c r="AS10">
-        <v>15.76348608040022</v>
+        <v>39.8645691473441</v>
       </c>
       <c r="AT10">
-        <v>69.38874233407432</v>
+        <v>58.36187574216106</v>
       </c>
       <c r="AU10">
-        <v>189.7227508916241</v>
+        <v>263.8686388997654</v>
       </c>
       <c r="AV10">
         <v>1</v>
@@ -1773,127 +1755,130 @@
         </is>
       </c>
       <c r="B11">
-        <v>268.2868415209515</v>
+        <v>318.7325877107284</v>
       </c>
       <c r="C11">
-        <v>92.24570288514802</v>
+        <v>99.58018862601645</v>
       </c>
       <c r="D11">
-        <v>5972.807827499785</v>
+        <v>6650.914866291366</v>
       </c>
       <c r="E11">
-        <v>106.8817326038466</v>
+        <v>134.4373418070505</v>
       </c>
       <c r="F11">
-        <v>253.2302687802361</v>
+        <v>293.0574037686495</v>
       </c>
       <c r="G11">
-        <v>10.3839065877501</v>
+        <v>23.29100169029511</v>
       </c>
       <c r="H11">
-        <v>27.27990337555123</v>
+        <v>27.57386099503913</v>
       </c>
       <c r="I11">
-        <v>215.6292466789758</v>
+        <v>237.59927002717</v>
       </c>
       <c r="J11">
-        <v>42.68227545137276</v>
+        <v>45.42809553913023</v>
       </c>
       <c r="K11">
-        <v>0.1961939365676583</v>
+        <v>0.1074401983122751</v>
       </c>
       <c r="L11">
-        <v>4267.45839661387</v>
+        <v>4769.201654290126</v>
       </c>
       <c r="M11">
-        <v>667.7433691433711</v>
+        <v>769.4104096926828</v>
       </c>
       <c r="N11">
-        <v>1037.606061742544</v>
+        <v>1112.302802308557</v>
       </c>
       <c r="O11">
-        <v>55.56142896739451</v>
+        <v>99.50527337437251</v>
       </c>
       <c r="P11">
-        <v>52.24811061879336</v>
+        <v>43.24644508654328</v>
+      </c>
+      <c r="Q11">
+        <v>0.05101405951883867</v>
       </c>
       <c r="S11">
-        <v>36.13021711886437</v>
+        <v>20.40888915948232</v>
       </c>
       <c r="T11">
-        <v>5.373840612551666</v>
+        <v>7.05489594799883</v>
       </c>
       <c r="U11">
-        <v>14.68810379295087</v>
+        <v>16.61549882393017</v>
       </c>
       <c r="V11">
-        <v>109.7769012510471</v>
+        <v>122.7824398062903</v>
       </c>
       <c r="W11">
-        <v>124.8695378425621</v>
+        <v>147.1115992188831</v>
       </c>
       <c r="Z11">
-        <v>0.2999551779887498</v>
+        <v>2.436851119263937</v>
       </c>
       <c r="AA11">
-        <v>6.779530656367613</v>
+        <v>21.53980798000725</v>
       </c>
       <c r="AB11">
-        <v>8.33727667619147</v>
+        <v>10.08551793444234</v>
       </c>
       <c r="AC11">
-        <v>9.148051573914142E-17</v>
+        <v>7.683167832258924E-16</v>
       </c>
       <c r="AD11">
-        <v>9.215029407883575</v>
+        <v>4.272685064935065</v>
       </c>
       <c r="AE11">
-        <v>16.82245008130391</v>
+        <v>0.1282782123186037</v>
       </c>
       <c r="AF11">
-        <v>42.9863300376846</v>
+        <v>41.25626565882223</v>
       </c>
       <c r="AG11">
-        <v>4.148498984005687</v>
+        <v>8.791194982583958</v>
       </c>
       <c r="AH11">
-        <v>1722.374723900568</v>
+        <v>1914.565532397556</v>
       </c>
       <c r="AJ11">
-        <v>103.601505063304</v>
+        <v>103.2032133339407</v>
       </c>
       <c r="AK11">
-        <v>729.5109812469994</v>
+        <v>830.6492503791078</v>
       </c>
       <c r="AL11">
-        <v>182.5043141729733</v>
+        <v>194.1622217705772</v>
       </c>
       <c r="AM11">
-        <v>1357.78913556763</v>
+        <v>1535.795672173236</v>
       </c>
       <c r="AN11">
-        <v>40.16226073558254</v>
+        <v>38.40382053523192</v>
       </c>
       <c r="AO11">
-        <v>132.1904231840841</v>
+        <v>152.4219437004756</v>
       </c>
       <c r="AP11">
-        <v>581.536989400268</v>
+        <v>666.5532137744224</v>
       </c>
       <c r="AQ11">
-        <v>34.48598006978476</v>
+        <v>39.95995900843643</v>
       </c>
       <c r="AR11">
-        <v>42.67492012107453</v>
+        <v>44.54157107925538</v>
       </c>
       <c r="AS11">
-        <v>0.9456433551419037</v>
+        <v>3.524119110437682</v>
       </c>
       <c r="AT11">
-        <v>51.53885553375594</v>
+        <v>1.623434422464218</v>
       </c>
       <c r="AU11">
-        <v>31.32778296247568</v>
+        <v>42.59205918893312</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -1906,133 +1891,133 @@
         </is>
       </c>
       <c r="B12">
-        <v>559.3178158875889</v>
+        <v>635.9576423575299</v>
       </c>
       <c r="C12">
-        <v>120.5939137880303</v>
+        <v>134.2013268511154</v>
       </c>
       <c r="D12">
-        <v>6690.01703874492</v>
+        <v>7421.00688504257</v>
       </c>
       <c r="E12">
-        <v>326.4285646352271</v>
+        <v>419.9405341995698</v>
       </c>
       <c r="F12">
-        <v>517.4649831836732</v>
+        <v>587.7017515407733</v>
       </c>
       <c r="G12">
-        <v>42.46924306166534</v>
+        <v>48.57452415415532</v>
       </c>
       <c r="H12">
-        <v>7.304036979846243</v>
+        <v>5.906751538980122</v>
       </c>
       <c r="I12">
-        <v>168.3608983466166</v>
+        <v>184.1910589354859</v>
       </c>
       <c r="J12">
-        <v>76.3884985169811</v>
+        <v>84.73251659398673</v>
       </c>
       <c r="K12">
-        <v>1.189180556738194</v>
+        <v>1.202312530062143</v>
       </c>
       <c r="L12">
-        <v>4163.582784353037</v>
+        <v>4691.867807084325</v>
       </c>
       <c r="M12">
-        <v>1762.618445267366</v>
+        <v>1880.311934955559</v>
       </c>
       <c r="N12">
-        <v>766.8342490939218</v>
+        <v>851.0366752411767</v>
       </c>
       <c r="O12">
-        <v>207.5648552398792</v>
+        <v>297.8787973958964</v>
       </c>
       <c r="P12">
-        <v>65.7823963747566</v>
+        <v>108.0163551956808</v>
       </c>
       <c r="Q12">
-        <v>2.383841222322468</v>
+        <v>2.143594943452089</v>
       </c>
       <c r="R12">
-        <v>8.969974893518955</v>
+        <v>9.187907008118041</v>
       </c>
       <c r="S12">
-        <v>73.46623803931823</v>
+        <v>59.29358193895882</v>
       </c>
       <c r="T12">
-        <v>68.21941192410914</v>
+        <v>76.44506982475801</v>
       </c>
       <c r="U12">
-        <v>59.12005355870424</v>
+        <v>73.36738311409319</v>
       </c>
       <c r="V12">
-        <v>245.2793268740402</v>
+        <v>264.9974848137865</v>
       </c>
       <c r="W12">
-        <v>144.9641008433606</v>
+        <v>171.2375580277482</v>
       </c>
       <c r="Z12">
-        <v>0.9371757304941631</v>
+        <v>5.270332338473252</v>
       </c>
       <c r="AA12">
-        <v>18.51226325928285</v>
+        <v>20.88901255489865</v>
       </c>
       <c r="AB12">
-        <v>26.82571802736989</v>
+        <v>30.65609844531507</v>
       </c>
       <c r="AC12">
-        <v>-8.319584872903121E-17</v>
+        <v>2.521289410518147E-17</v>
       </c>
       <c r="AD12">
-        <v>0.14210313673742</v>
+        <v>6.092647874349003</v>
       </c>
       <c r="AE12">
-        <v>7.667615309208547</v>
+        <v>6.128828749923007</v>
       </c>
       <c r="AF12">
-        <v>13.46047547671393</v>
+        <v>6.048210987407256</v>
       </c>
       <c r="AG12">
-        <v>5.866912234611815</v>
+        <v>4.253247242372497</v>
       </c>
       <c r="AH12">
-        <v>3130.805540316365</v>
+        <v>3524.386772306313</v>
       </c>
       <c r="AJ12">
-        <v>249.6313297438916</v>
+        <v>254.0507675740037</v>
       </c>
       <c r="AK12">
-        <v>576.6275563156247</v>
+        <v>680.0702423364277</v>
       </c>
       <c r="AL12">
-        <v>79.84835759858646</v>
+        <v>81.93064380452589</v>
       </c>
       <c r="AM12">
-        <v>51.5591667477426</v>
+        <v>56.92835263920217</v>
       </c>
       <c r="AN12">
-        <v>32.80314358447182</v>
+        <v>36.16172790141364</v>
       </c>
       <c r="AO12">
-        <v>74.67090672407186</v>
+        <v>70.00518168784201</v>
       </c>
       <c r="AP12">
-        <v>1199.994435847319</v>
+        <v>1246.600262214744</v>
       </c>
       <c r="AQ12">
-        <v>178.1785496160331</v>
+        <v>195.739410788379</v>
       </c>
       <c r="AR12">
-        <v>233.2494939038591</v>
+        <v>267.3865082406565</v>
       </c>
       <c r="AS12">
-        <v>12.96720980003402</v>
+        <v>14.0125771381866</v>
       </c>
       <c r="AT12">
-        <v>26.24968432468973</v>
+        <v>76.7955829353841</v>
       </c>
       <c r="AU12">
-        <v>135.8162136283985</v>
+        <v>149.4889290294792</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2045,130 +2030,130 @@
         </is>
       </c>
       <c r="B13">
-        <v>1340.65503372542</v>
+        <v>1528.561575949731</v>
       </c>
       <c r="C13">
-        <v>270.7872736579181</v>
+        <v>272.9895896526779</v>
       </c>
       <c r="D13">
-        <v>7879.125359733186</v>
+        <v>8479.28466941879</v>
       </c>
       <c r="E13">
-        <v>396.3526406934384</v>
+        <v>459.7067140096966</v>
       </c>
       <c r="F13">
-        <v>1259.759835951065</v>
+        <v>1440.055287815629</v>
       </c>
       <c r="G13">
-        <v>78.7379653279355</v>
+        <v>88.16999710656772</v>
       </c>
       <c r="H13">
-        <v>9.46785351484281</v>
+        <v>1.771132745016712</v>
       </c>
       <c r="I13">
-        <v>244.8764762539889</v>
+        <v>252.4811462976237</v>
       </c>
       <c r="J13">
-        <v>113.9440417526634</v>
+        <v>113.1511868824259</v>
       </c>
       <c r="K13">
-        <v>3.708660430486174</v>
+        <v>0.1176482951379258</v>
       </c>
       <c r="L13">
-        <v>3205.293563413023</v>
+        <v>3660.357325213735</v>
       </c>
       <c r="M13">
-        <v>3455.979844260671</v>
+        <v>3526.792634340498</v>
       </c>
       <c r="N13">
-        <v>1217.851952059493</v>
+        <v>1292.134709864557</v>
       </c>
       <c r="O13">
-        <v>269.0254484516527</v>
+        <v>335.8895936455429</v>
       </c>
       <c r="P13">
-        <v>63.11230225821971</v>
+        <v>77.60740605394435</v>
       </c>
       <c r="Q13">
-        <v>2.681294592469116</v>
+        <v>2.710531825651398</v>
       </c>
       <c r="R13">
-        <v>24.96507945902755</v>
+        <v>14.27238282378778</v>
       </c>
       <c r="S13">
-        <v>90.95931167398427</v>
+        <v>88.16812547500497</v>
       </c>
       <c r="T13">
-        <v>156.7199241474421</v>
+        <v>182.9200999503024</v>
       </c>
       <c r="U13">
-        <v>290.434734681201</v>
+        <v>342.4422335398873</v>
       </c>
       <c r="V13">
-        <v>467.8437208003546</v>
+        <v>545.4720827939356</v>
       </c>
       <c r="W13">
-        <v>320.9995031725086</v>
+        <v>369.4784555833429</v>
       </c>
       <c r="Z13">
-        <v>50.91200863506591</v>
+        <v>13.55570587872654</v>
       </c>
       <c r="AA13">
-        <v>32.91736798704311</v>
+        <v>37.73029824460362</v>
       </c>
       <c r="AB13">
-        <v>49.36141294483165</v>
+        <v>53.12981613460219</v>
       </c>
       <c r="AC13">
-        <v>2.83274156923678E-16</v>
+        <v>-1.163413555980206E-15</v>
       </c>
       <c r="AD13">
-        <v>1.827043230834037</v>
-      </c>
-      <c r="AF13">
-        <v>73.51640203284198</v>
+        <v>3.109346764838182</v>
+      </c>
+      <c r="AE13">
+        <v>2.517527938789705</v>
       </c>
       <c r="AG13">
-        <v>0.9921671605686123</v>
+        <v>0.326290840370528</v>
       </c>
       <c r="AH13">
-        <v>2114.048189922615</v>
+        <v>2335.244742688585</v>
       </c>
       <c r="AJ13">
-        <v>96.9034790788667</v>
+        <v>98.87599577074651</v>
       </c>
       <c r="AK13">
-        <v>453.6777219419313</v>
+        <v>598.0317391648043</v>
       </c>
       <c r="AL13">
-        <v>104.2144280842565</v>
+        <v>114.8876781768922</v>
       </c>
       <c r="AM13">
-        <v>35.14456372718967</v>
+        <v>44.50408554347892</v>
       </c>
       <c r="AN13">
-        <v>29.60957857280232</v>
+        <v>28.10643864615673</v>
       </c>
       <c r="AO13">
-        <v>397.9531539291253</v>
+        <v>454.6016012622471</v>
       </c>
       <c r="AP13">
-        <v>2687.438379251278</v>
+        <v>2728.421705995496</v>
       </c>
       <c r="AQ13">
-        <v>152.6332523670808</v>
+        <v>158.3903991065302</v>
       </c>
       <c r="AR13">
-        <v>208.6226531256034</v>
+        <v>205.1280460691609</v>
       </c>
       <c r="AS13">
-        <v>23.45946744897437</v>
+        <v>27.8877925295753</v>
       </c>
       <c r="AT13">
-        <v>60.87141863880069</v>
+        <v>87.65153772889018</v>
       </c>
       <c r="AU13">
-        <v>381.9723387068315</v>
+        <v>396.8781063379591</v>
       </c>
       <c r="AV13">
         <v>1</v>
@@ -2181,130 +2166,130 @@
         </is>
       </c>
       <c r="B14">
-        <v>1205.109825129967</v>
+        <v>1394.395683364409</v>
       </c>
       <c r="C14">
-        <v>287.281530188307</v>
+        <v>298.3830888369537</v>
       </c>
       <c r="D14">
-        <v>8470.13650957145</v>
+        <v>9803.339120914075</v>
       </c>
       <c r="E14">
-        <v>478.0235391171644</v>
+        <v>540.5631098915642</v>
       </c>
       <c r="F14">
-        <v>1129.848826635405</v>
+        <v>1308.366447289934</v>
       </c>
       <c r="G14">
-        <v>69.66597338549289</v>
+        <v>79.9435492507365</v>
       </c>
       <c r="H14">
-        <v>19.94124333744985</v>
+        <v>21.60945136379287</v>
       </c>
       <c r="I14">
-        <v>239.2324085556787</v>
+        <v>267.7352360745447</v>
       </c>
       <c r="J14">
-        <v>90.90053491495965</v>
+        <v>94.62030381818064</v>
       </c>
       <c r="K14">
-        <v>30.54397812778916</v>
+        <v>8.253887993201079</v>
       </c>
       <c r="L14">
-        <v>3562.382894722099</v>
+        <v>3995.155849193381</v>
       </c>
       <c r="M14">
-        <v>3792.778401013815</v>
+        <v>4511.68493271653</v>
       </c>
       <c r="N14">
-        <v>1114.975213835537</v>
+        <v>1296.498339004165</v>
       </c>
       <c r="O14">
-        <v>302.5229528680686</v>
+        <v>339.0797619044193</v>
       </c>
       <c r="P14">
-        <v>106.2090584776953</v>
+        <v>122.9334257907968</v>
       </c>
       <c r="Q14">
-        <v>0.02023748723186925</v>
+        <v>1.085587067997094</v>
       </c>
       <c r="S14">
-        <v>86.10144898738658</v>
+        <v>103.8357983797181</v>
       </c>
       <c r="T14">
-        <v>134.4250296979078</v>
+        <v>165.1275984536931</v>
       </c>
       <c r="U14">
-        <v>284.5807806027972</v>
+        <v>311.0444595090846</v>
       </c>
       <c r="V14">
-        <v>417.5474264931952</v>
+        <v>477.8768701586687</v>
       </c>
       <c r="W14">
-        <v>284.2616942488556</v>
+        <v>351.6153416875062</v>
       </c>
       <c r="Z14">
-        <v>18.29756723807699</v>
+        <v>8.54911689686357</v>
       </c>
       <c r="AA14">
-        <v>39.14356818739899</v>
+        <v>44.78986584591878</v>
       </c>
       <c r="AB14">
-        <v>32.78229343682142</v>
+        <v>36.56898569081153</v>
       </c>
       <c r="AC14">
-        <v>-8.030208078625636E-16</v>
+        <v>-5.140588069350847E-17</v>
       </c>
       <c r="AD14">
-        <v>13.19283529412405</v>
+        <v>15.71861767645358</v>
       </c>
       <c r="AE14">
-        <v>1.697726301449113</v>
+        <v>7.192318955928982</v>
       </c>
       <c r="AF14">
-        <v>56.14442071323793</v>
+        <v>54.53036894292354</v>
       </c>
       <c r="AG14">
-        <v>6.273884905907834</v>
+        <v>0.2823638017250977</v>
       </c>
       <c r="AH14">
-        <v>2360.302918094636</v>
+        <v>2581.981615623111</v>
       </c>
       <c r="AJ14">
-        <v>115.2455894294397</v>
+        <v>145.5289301513234</v>
       </c>
       <c r="AK14">
-        <v>499.5646017434906</v>
+        <v>608.0545677318486</v>
       </c>
       <c r="AL14">
-        <v>105.9880771482916</v>
+        <v>111.1414208628443</v>
       </c>
       <c r="AM14">
-        <v>39.60219115228629</v>
+        <v>60.28820769942612</v>
       </c>
       <c r="AN14">
-        <v>29.73332906996746</v>
+        <v>30.9574943881864</v>
       </c>
       <c r="AO14">
-        <v>432.2919366794732</v>
+        <v>464.5239716894279</v>
       </c>
       <c r="AP14">
-        <v>2830.009096648654</v>
+        <v>3421.143945227376</v>
       </c>
       <c r="AQ14">
-        <v>182.1845023100899</v>
+        <v>211.0647547527794</v>
       </c>
       <c r="AR14">
-        <v>245.2161986242664</v>
+        <v>313.1197214053221</v>
       </c>
       <c r="AS14">
-        <v>10.7795250743908</v>
+        <v>11.4393156894799</v>
       </c>
       <c r="AT14">
-        <v>30.39922338532962</v>
+        <v>86.15095166396365</v>
       </c>
       <c r="AU14">
-        <v>528.3240743786172</v>
+        <v>520.5226103350665</v>
       </c>
       <c r="AV14">
         <v>1</v>
@@ -2317,127 +2302,127 @@
         </is>
       </c>
       <c r="B15">
-        <v>459.2060317357015</v>
+        <v>475.1053670414807</v>
       </c>
       <c r="C15">
-        <v>108.8467745293965</v>
+        <v>107.6486137744406</v>
       </c>
       <c r="D15">
-        <v>5337.190238863629</v>
+        <v>6013.394005850463</v>
       </c>
       <c r="E15">
-        <v>93.71588198977786</v>
+        <v>140.0080824030472</v>
       </c>
       <c r="F15">
-        <v>421.429748116895</v>
+        <v>436.3991994009299</v>
       </c>
       <c r="G15">
-        <v>31.30776901782954</v>
+        <v>33.50032345256311</v>
       </c>
       <c r="H15">
-        <v>28.06575732304209</v>
+        <v>26.23745470745819</v>
       </c>
       <c r="I15">
-        <v>190.0037872932759</v>
+        <v>197.8987299971272</v>
       </c>
       <c r="J15">
-        <v>64.92630457398036</v>
+        <v>62.51381570492039</v>
       </c>
       <c r="K15">
-        <v>-3.221401827854498E-15</v>
+        <v>-7.08522302618731E-15</v>
       </c>
       <c r="L15">
-        <v>3291.926336546385</v>
+        <v>3883.476791521656</v>
       </c>
       <c r="M15">
-        <v>1043.201310023131</v>
+        <v>1089.028781592539</v>
       </c>
       <c r="N15">
-        <v>1002.062592294113</v>
+        <v>1040.888432736268</v>
       </c>
       <c r="O15">
-        <v>61.78085147148306</v>
+        <v>106.8244741268239</v>
       </c>
       <c r="P15">
-        <v>20.50385399051009</v>
+        <v>19.69092980349814</v>
       </c>
       <c r="S15">
-        <v>22.23570002682244</v>
+        <v>23.65069781579957</v>
       </c>
       <c r="T15">
-        <v>29.425381620867</v>
+        <v>21.59153431203467</v>
       </c>
       <c r="U15">
-        <v>21.21675257563933</v>
+        <v>23.6502280061936</v>
       </c>
       <c r="V15">
-        <v>199.8653465400913</v>
+        <v>193.4033695304267</v>
       </c>
       <c r="W15">
-        <v>173.8156172323979</v>
+        <v>200.9788523917395</v>
       </c>
       <c r="Z15">
-        <v>0.2087951689214287</v>
+        <v>0.06291593012461295</v>
       </c>
       <c r="AA15">
-        <v>22.44819328111731</v>
+        <v>23.53587743080461</v>
       </c>
       <c r="AB15">
-        <v>11.38158433687314</v>
+        <v>12.98533712937002</v>
       </c>
       <c r="AC15">
-        <v>9.703200147151792E-16</v>
+        <v>7.307972697119744E-16</v>
       </c>
       <c r="AD15">
-        <v>0.8606756868344869</v>
+        <v>1.03155306216269</v>
       </c>
       <c r="AE15">
-        <v>12.8013163028547</v>
+        <v>0.1647420872935314</v>
       </c>
       <c r="AF15">
-        <v>35.72199528960154</v>
+        <v>32.55859076732783</v>
       </c>
       <c r="AG15">
-        <v>12.74737577073659</v>
+        <v>5.013613556515284</v>
       </c>
       <c r="AH15">
-        <v>1236.070919408729</v>
+        <v>1414.311031845099</v>
       </c>
       <c r="AJ15">
-        <v>203.6207481643305</v>
+        <v>221.7006899327004</v>
       </c>
       <c r="AK15">
-        <v>621.642178097071</v>
+        <v>720.7921937163848</v>
       </c>
       <c r="AL15">
-        <v>174.9167526803711</v>
+        <v>190.4414575044852</v>
       </c>
       <c r="AM15">
-        <v>919.2477026079633</v>
+        <v>1165.398330848308</v>
       </c>
       <c r="AN15">
-        <v>25.66507152624225</v>
+        <v>27.64933578343542</v>
       </c>
       <c r="AO15">
-        <v>115.4369654007537</v>
+        <v>152.6523841660987</v>
       </c>
       <c r="AP15">
-        <v>854.3499013365256</v>
+        <v>881.0289379879179</v>
       </c>
       <c r="AQ15">
-        <v>45.1051461273907</v>
+        <v>48.63499276498514</v>
       </c>
       <c r="AR15">
-        <v>35.5484701178064</v>
+        <v>32.38439920628989</v>
       </c>
       <c r="AS15">
-        <v>7.512935730526122</v>
+        <v>7.706429755282281</v>
       </c>
       <c r="AT15">
-        <v>78.87969386382964</v>
+        <v>101.4534088611079</v>
       </c>
       <c r="AU15">
-        <v>103.3767792230064</v>
+        <v>116.8005401918979</v>
       </c>
       <c r="AV15">
         <v>1</v>
@@ -2450,121 +2435,124 @@
         </is>
       </c>
       <c r="B16">
-        <v>306.786983318553</v>
+        <v>379.4155540238518</v>
       </c>
       <c r="C16">
-        <v>116.0459575102837</v>
+        <v>134.1544056181487</v>
       </c>
       <c r="D16">
-        <v>7023.23273227156</v>
+        <v>7748.627321036065</v>
       </c>
       <c r="E16">
-        <v>184.2897123489157</v>
+        <v>245.9490811746833</v>
       </c>
       <c r="F16">
-        <v>296.5627265075021</v>
+        <v>367.5497615346996</v>
       </c>
       <c r="G16">
-        <v>9.236479952018861</v>
+        <v>10.89874544438861</v>
       </c>
       <c r="H16">
-        <v>42.72836944249214</v>
+        <v>45.18307473629735</v>
       </c>
       <c r="I16">
-        <v>172.2241787819562</v>
+        <v>207.1331987580212</v>
       </c>
       <c r="J16">
-        <v>45.18069671553517</v>
+        <v>46.66963840732476</v>
       </c>
       <c r="K16">
-        <v>4.054684973352726</v>
+        <v>3.853790141072231</v>
       </c>
       <c r="L16">
-        <v>5064.465803521188</v>
+        <v>5655.750772645161</v>
       </c>
       <c r="M16">
-        <v>748.7039443112383</v>
+        <v>793.243764352591</v>
       </c>
       <c r="N16">
-        <v>1210.062984439134</v>
+        <v>1299.632784038313</v>
       </c>
       <c r="O16">
-        <v>129.6747070696879</v>
+        <v>201.890044899241</v>
       </c>
       <c r="P16">
-        <v>21.52823204596805</v>
+        <v>20.00849071406119</v>
+      </c>
+      <c r="Q16">
+        <v>33.71763317599461</v>
       </c>
       <c r="S16">
-        <v>50.75332009444854</v>
+        <v>40.10502816223625</v>
       </c>
       <c r="T16">
-        <v>15.29242850607079</v>
+        <v>17.61476387404759</v>
       </c>
       <c r="U16">
-        <v>12.11036949829531</v>
+        <v>14.57025360273143</v>
       </c>
       <c r="V16">
-        <v>115.7816349136269</v>
+        <v>140.1103401983291</v>
       </c>
       <c r="W16">
-        <v>154.6656303052063</v>
+        <v>196.9300969859272</v>
       </c>
       <c r="Z16">
-        <v>0.0828948277547418</v>
+        <v>0.09454674044410333</v>
       </c>
       <c r="AA16">
-        <v>6.313714735266116</v>
+        <v>7.066658456748383</v>
       </c>
       <c r="AB16">
-        <v>5.778979362467518</v>
+        <v>6.896860997656432</v>
       </c>
       <c r="AC16">
-        <v>7.772316748618677E-17</v>
+        <v>6.449656078781993E-17</v>
       </c>
       <c r="AF16">
-        <v>54.5977094447279</v>
+        <v>59.43158657412276</v>
       </c>
       <c r="AG16">
-        <v>1.185679434666958</v>
+        <v>2.437539222821127</v>
       </c>
       <c r="AH16">
-        <v>3324.318425076093</v>
+        <v>3675.21750031994</v>
       </c>
       <c r="AJ16">
-        <v>96.34608052237415</v>
+        <v>82.61082638839591</v>
       </c>
       <c r="AK16">
-        <v>878.9677882547803</v>
+        <v>995.898068655364</v>
       </c>
       <c r="AL16">
-        <v>158.0724352825902</v>
+        <v>156.0597382561055</v>
       </c>
       <c r="AM16">
-        <v>440.8489223113446</v>
+        <v>573.606545293015</v>
       </c>
       <c r="AN16">
-        <v>74.38659162653123</v>
+        <v>67.7709779867744</v>
       </c>
       <c r="AO16">
-        <v>92.73406159078289</v>
+        <v>105.6657853324349</v>
       </c>
       <c r="AP16">
-        <v>647.7203834578572</v>
+        <v>676.2041743139666</v>
       </c>
       <c r="AQ16">
-        <v>34.00760267412436</v>
+        <v>38.3443248121819</v>
       </c>
       <c r="AR16">
-        <v>14.96372435339439</v>
+        <v>18.21096932871417</v>
       </c>
       <c r="AS16">
-        <v>6.096770504040815</v>
+        <v>7.488004740079988</v>
       </c>
       <c r="AT16">
-        <v>12.66859593365553</v>
+        <v>45.62358850734597</v>
       </c>
       <c r="AU16">
-        <v>51.30215569754676</v>
+        <v>57.05262736568975</v>
       </c>
       <c r="AV16">
         <v>1</v>
@@ -2577,124 +2565,124 @@
         </is>
       </c>
       <c r="B17">
-        <v>308.1597604170155</v>
+        <v>354.3527335558614</v>
       </c>
       <c r="C17">
-        <v>184.9302515976536</v>
+        <v>183.6073101036295</v>
       </c>
       <c r="D17">
-        <v>4999.372284330724</v>
+        <v>5486.017119412244</v>
       </c>
       <c r="E17">
-        <v>170.6006763717683</v>
+        <v>211.8686460155528</v>
       </c>
       <c r="F17">
-        <v>285.2004929766968</v>
+        <v>327.8487477719941</v>
       </c>
       <c r="G17">
-        <v>22.70771831002244</v>
+        <v>25.95657855824361</v>
       </c>
       <c r="H17">
-        <v>11.50837271105938</v>
+        <v>11.19143661275201</v>
       </c>
       <c r="I17">
-        <v>175.0552732858466</v>
+        <v>167.6174675397392</v>
       </c>
       <c r="J17">
-        <v>45.50157428227902</v>
+        <v>47.54725496887756</v>
       </c>
       <c r="K17">
-        <v>0.1775281569126005</v>
+        <v>0.1719093349209927</v>
       </c>
       <c r="L17">
-        <v>3184.491112516595</v>
+        <v>3543.635018513246</v>
       </c>
       <c r="M17">
-        <v>850.6596664229887</v>
+        <v>943.0264941922993</v>
       </c>
       <c r="N17">
-        <v>964.2215053911412</v>
+        <v>999.3556067066985</v>
       </c>
       <c r="O17">
-        <v>87.52812834653588</v>
+        <v>149.8835152916071</v>
       </c>
       <c r="P17">
-        <v>25.34223742606975</v>
+        <v>24.85275274234424</v>
       </c>
       <c r="S17">
-        <v>71.50326572202663</v>
+        <v>50.77437812821439</v>
       </c>
       <c r="T17">
-        <v>32.1732938375215</v>
+        <v>36.22821974782677</v>
       </c>
       <c r="U17">
-        <v>14.42809056996565</v>
+        <v>18.40312047426113</v>
       </c>
       <c r="V17">
-        <v>116.6155775856518</v>
+        <v>130.2795079943201</v>
       </c>
       <c r="W17">
-        <v>122.4016576593124</v>
+        <v>143.3709142802098</v>
       </c>
       <c r="Z17">
-        <v>0.2529567294459285</v>
+        <v>0.3824339589636789</v>
       </c>
       <c r="AA17">
-        <v>13.01889608791089</v>
+        <v>14.40292812431231</v>
       </c>
       <c r="AB17">
-        <v>11.82228132793391</v>
+        <v>13.31865987616106</v>
       </c>
       <c r="AC17">
-        <v>1.556047009368811E-16</v>
+        <v>-9.756113915684725E-17</v>
       </c>
       <c r="AE17">
-        <v>0.9010921793683611</v>
+        <v>0.9436809027281817</v>
       </c>
       <c r="AF17">
-        <v>24.74892429279307</v>
+        <v>13.54241604247699</v>
       </c>
       <c r="AG17">
-        <v>10.19173718603804</v>
+        <v>12.11573608784766</v>
       </c>
       <c r="AH17">
-        <v>1850.319725097523</v>
+        <v>2061.075721134765</v>
       </c>
       <c r="AJ17">
-        <v>49.24276724299966</v>
+        <v>50.66556900835678</v>
       </c>
       <c r="AK17">
-        <v>675.707461578162</v>
+        <v>753.2334943266901</v>
       </c>
       <c r="AL17">
-        <v>124.726833165591</v>
+        <v>123.7015609832316</v>
       </c>
       <c r="AM17">
-        <v>330.5010772749943</v>
+        <v>447.0637155813886</v>
       </c>
       <c r="AN17">
-        <v>36.52995639503473</v>
+        <v>35.41650063992073</v>
       </c>
       <c r="AO17">
-        <v>119.4580256409309</v>
+        <v>72.67093782063239</v>
       </c>
       <c r="AP17">
-        <v>706.2776584421824</v>
+        <v>769.0880350146862</v>
       </c>
       <c r="AQ17">
-        <v>52.70513168872091</v>
+        <v>64.53642116995017</v>
       </c>
       <c r="AR17">
-        <v>9.747536870673679</v>
+        <v>16.76908723759891</v>
       </c>
       <c r="AS17">
-        <v>14.89165890226013</v>
+        <v>21.79835002396079</v>
       </c>
       <c r="AT17">
-        <v>30.43634525239657</v>
+        <v>19.79060652726094</v>
       </c>
       <c r="AU17">
-        <v>71.24583797986783</v>
+        <v>77.6293538667157</v>
       </c>
       <c r="AV17">
         <v>1</v>
@@ -2707,121 +2695,124 @@
         </is>
       </c>
       <c r="B18">
-        <v>343.6414715458861</v>
+        <v>429.6453507468882</v>
       </c>
       <c r="C18">
-        <v>116.7994603616349</v>
+        <v>126.3156274146282</v>
       </c>
       <c r="D18">
-        <v>6914.175901842998</v>
+        <v>7893.320919945343</v>
       </c>
       <c r="E18">
-        <v>232.4693795299572</v>
+        <v>210.1402185134369</v>
       </c>
       <c r="F18">
-        <v>334.0171861603462</v>
+        <v>418.4641140278596</v>
       </c>
       <c r="G18">
-        <v>10.2711639941489</v>
+        <v>10.65996334144459</v>
       </c>
       <c r="H18">
-        <v>32.87460185708364</v>
+        <v>45.26523181662782</v>
       </c>
       <c r="I18">
-        <v>189.252582178036</v>
+        <v>189.9203097340886</v>
       </c>
       <c r="J18">
-        <v>56.49200277308594</v>
+        <v>65.07225695793278</v>
       </c>
       <c r="K18">
-        <v>4.742831305616417</v>
+        <v>0.07087164463178135</v>
       </c>
       <c r="L18">
-        <v>4892.090226699615</v>
+        <v>5742.425055580377</v>
       </c>
       <c r="M18">
-        <v>872.3930483227672</v>
+        <v>902.7702746776617</v>
       </c>
       <c r="N18">
-        <v>1149.692626820615</v>
+        <v>1248.125589687304</v>
       </c>
       <c r="O18">
-        <v>139.2693617329215</v>
+        <v>169.8343890796851</v>
       </c>
       <c r="P18">
-        <v>377.3888860209275</v>
+        <v>26.23621485282043</v>
       </c>
       <c r="S18">
-        <v>29.76070786217585</v>
+        <v>35.39402665308685</v>
       </c>
       <c r="T18">
-        <v>7.02748690256455</v>
+        <v>8.957394090389529</v>
       </c>
       <c r="U18">
-        <v>10.98916555373992</v>
+        <v>13.63845131019322</v>
       </c>
       <c r="V18">
-        <v>149.9338833089061</v>
+        <v>200.1680049784581</v>
       </c>
       <c r="W18">
-        <v>166.4888890393163</v>
+        <v>196.3917901350173</v>
       </c>
       <c r="Z18">
-        <v>1.27718232741219</v>
+        <v>0.7742104280145806</v>
       </c>
       <c r="AA18">
-        <v>6.280629937269332</v>
+        <v>7.137028385718112</v>
       </c>
       <c r="AB18">
-        <v>6.990400707964574</v>
+        <v>6.209808027191561</v>
       </c>
       <c r="AC18">
-        <v>-1.944449981698277E-16</v>
+        <v>1.987432063814836E-16</v>
+      </c>
+      <c r="AE18">
+        <v>1.465901960784314</v>
       </c>
       <c r="AF18">
-        <v>73.81835243042657</v>
+        <v>104.8494683184325</v>
       </c>
       <c r="AG18">
-        <v>9.47817295803053</v>
+        <v>12.84229579139863</v>
       </c>
       <c r="AH18">
-        <v>2773.229561573746</v>
+        <v>3102.636923803904</v>
       </c>
       <c r="AJ18">
-        <v>65.00814618171609</v>
+        <v>58.34804118255609</v>
       </c>
       <c r="AK18">
-        <v>812.6879738205837</v>
+        <v>1055.280661545781</v>
       </c>
       <c r="AL18">
-        <v>201.3101658512555</v>
+        <v>187.8554097099199</v>
       </c>
       <c r="AM18">
-        <v>828.666776511791</v>
+        <v>1114.4423415445</v>
       </c>
       <c r="AN18">
-        <v>124.0951860426213</v>
+        <v>119.9686562983284</v>
       </c>
       <c r="AO18">
-        <v>138.1968836204755</v>
+        <v>104.7072529907342</v>
       </c>
       <c r="AP18">
-        <v>723.4141925525178</v>
+        <v>794.186663787202</v>
       </c>
       <c r="AQ18">
-        <v>32.26634107968589</v>
+        <v>39.75720581043812</v>
       </c>
       <c r="AR18">
-        <v>75.804096700283</v>
+        <v>28.64960850468716</v>
       </c>
       <c r="AS18">
-        <v>5.712408066496208</v>
+        <v>6.990108591644944</v>
       </c>
       <c r="AT18">
-        <v>9.914121942103515</v>
+        <v>0.492566705111465</v>
       </c>
       <c r="AU18">
-        <v>70.41578556034011</v>
+        <v>42.56256873981617</v>
       </c>
       <c r="AV18">
         <v>1</v>
@@ -2834,130 +2825,130 @@
         </is>
       </c>
       <c r="B19">
-        <v>813.0150276083922</v>
+        <v>976.0242920157862</v>
       </c>
       <c r="C19">
-        <v>271.7774555486627</v>
+        <v>270.9515228021964</v>
       </c>
       <c r="D19">
-        <v>6807.455885105423</v>
+        <v>7492.955644707528</v>
       </c>
       <c r="E19">
-        <v>662.3468139723891</v>
+        <v>871.203589034183</v>
       </c>
       <c r="F19">
-        <v>730.8300199419215</v>
+        <v>873.8255846853172</v>
       </c>
       <c r="G19">
-        <v>79.70474650773673</v>
+        <v>94.24320197952296</v>
       </c>
       <c r="H19">
-        <v>8.329260790259578</v>
+        <v>25.66515204522582</v>
       </c>
       <c r="I19">
-        <v>328.8865309312581</v>
+        <v>375.8625181183115</v>
       </c>
       <c r="J19">
-        <v>96.77840864523954</v>
+        <v>100.9148117134511</v>
       </c>
       <c r="K19">
-        <v>103.0294294433259</v>
+        <v>8.94761162926909</v>
       </c>
       <c r="L19">
-        <v>3882.927763480561</v>
+        <v>4329.897670921562</v>
       </c>
       <c r="M19">
-        <v>2072.602750931359</v>
+        <v>2262.235294188189</v>
       </c>
       <c r="N19">
-        <v>851.9253706935024</v>
+        <v>900.8226795977768</v>
       </c>
       <c r="O19">
-        <v>457.5377734304228</v>
+        <v>627.434018940983</v>
       </c>
       <c r="P19">
-        <v>102.2789697252265</v>
+        <v>138.1313082622489</v>
       </c>
       <c r="Q19">
-        <v>7.343668814182406</v>
+        <v>6.921312955641977</v>
       </c>
       <c r="R19">
-        <v>1.787890257588648</v>
+        <v>1.041897762916584</v>
       </c>
       <c r="S19">
-        <v>115.5025753907528</v>
+        <v>130.7859342410308</v>
       </c>
       <c r="T19">
-        <v>153.6750004779365</v>
+        <v>179.9506410743442</v>
       </c>
       <c r="U19">
-        <v>113.2296048287508</v>
+        <v>129.0029670936583</v>
       </c>
       <c r="V19">
-        <v>229.6604294240862</v>
+        <v>277.1246801823983</v>
       </c>
       <c r="W19">
-        <v>234.0852177512019</v>
+        <v>286.7111406459457</v>
       </c>
       <c r="Z19">
-        <v>3.299610877021422</v>
+        <v>1.937421613968987</v>
       </c>
       <c r="AA19">
-        <v>26.00918176457087</v>
+        <v>30.55513512454185</v>
       </c>
       <c r="AB19">
-        <v>55.58772242680706</v>
+        <v>65.16466540816378</v>
       </c>
       <c r="AC19">
-        <v>1.650411277446647E-15</v>
+        <v>-1.067613514468407E-15</v>
       </c>
       <c r="AD19">
-        <v>3.691927760154256</v>
+        <v>15.97727585174803</v>
       </c>
       <c r="AF19">
-        <v>16.14533148194797</v>
+        <v>13.47877030885351</v>
       </c>
       <c r="AG19">
-        <v>31.41467137307395</v>
+        <v>79.86686066667296</v>
       </c>
       <c r="AH19">
-        <v>3014.025153787346</v>
+        <v>3388.334067822414</v>
       </c>
       <c r="AJ19">
-        <v>107.6389615501287</v>
+        <v>100.7332056316056</v>
       </c>
       <c r="AK19">
-        <v>400.3344514261554</v>
+        <v>435.6238176047293</v>
       </c>
       <c r="AL19">
-        <v>90.57445806365219</v>
+        <v>89.978431798671</v>
       </c>
       <c r="AM19">
-        <v>26.50526099123362</v>
+        <v>50.6593289244055</v>
       </c>
       <c r="AN19">
-        <v>29.47019822365968</v>
+        <v>34.15301745536157</v>
       </c>
       <c r="AO19">
-        <v>243.5970900392391</v>
+        <v>244.2911116575349</v>
       </c>
       <c r="AP19">
-        <v>1668.112289822819</v>
+        <v>1742.188091148902</v>
       </c>
       <c r="AQ19">
-        <v>212.8809355824115</v>
+        <v>226.7861354171087</v>
       </c>
       <c r="AR19">
-        <v>74.06581423971836</v>
+        <v>81.84302045990877</v>
       </c>
       <c r="AS19">
-        <v>21.00716058975033</v>
+        <v>60.42742990914245</v>
       </c>
       <c r="AT19">
-        <v>8.62550350173383</v>
+        <v>9.45701318928346</v>
       </c>
       <c r="AU19">
-        <v>116.0188986711899</v>
+        <v>167.7903642739971</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2970,127 +2961,127 @@
         </is>
       </c>
       <c r="B20">
-        <v>1157.369226753835</v>
+        <v>1302.528744808133</v>
       </c>
       <c r="C20">
-        <v>275.3646706071116</v>
+        <v>312.7202948024716</v>
       </c>
       <c r="D20">
-        <v>7366.452549905876</v>
+        <v>8542.324509769967</v>
       </c>
       <c r="E20">
-        <v>583.6781852223017</v>
+        <v>691.3150512194718</v>
       </c>
       <c r="F20">
-        <v>1080.172970975859</v>
+        <v>1218.16613498261</v>
       </c>
       <c r="G20">
-        <v>75.27905029114049</v>
+        <v>84.77310319762761</v>
       </c>
       <c r="H20">
-        <v>41.62412493219692</v>
+        <v>16.62705552292083</v>
       </c>
       <c r="I20">
-        <v>231.045787188335</v>
+        <v>264.8440938233483</v>
       </c>
       <c r="J20">
-        <v>76.79976805231276</v>
+        <v>87.58133598729383</v>
       </c>
       <c r="K20">
-        <v>0.04536494520399417</v>
+        <v>0.3407633428009137</v>
       </c>
       <c r="L20">
-        <v>4350.736102463063</v>
+        <v>5030.387783290327</v>
       </c>
       <c r="M20">
-        <v>2220.324102554953</v>
+        <v>2600.558162834371</v>
       </c>
       <c r="N20">
-        <v>795.3923448878611</v>
+        <v>911.3785636452682</v>
       </c>
       <c r="O20">
-        <v>419.3271290900421</v>
+        <v>543.6396347054947</v>
       </c>
       <c r="P20">
-        <v>64.81517461508042</v>
+        <v>55.10586420646979</v>
       </c>
       <c r="Q20">
-        <v>0.868692962433003</v>
+        <v>1.869257194710915</v>
       </c>
       <c r="R20">
-        <v>0.2530447830817162</v>
+        <v>0.4500406805860108</v>
       </c>
       <c r="S20">
-        <v>124.430595177337</v>
+        <v>116.5295249870848</v>
       </c>
       <c r="T20">
-        <v>226.2732565046502</v>
+        <v>260.8298481635896</v>
       </c>
       <c r="U20">
-        <v>52.46612131200185</v>
+        <v>63.48807385412292</v>
       </c>
       <c r="V20">
-        <v>485.0992610160333</v>
+        <v>555.5508202274164</v>
       </c>
       <c r="W20">
-        <v>312.6436037459415</v>
+        <v>347.7003708979224</v>
       </c>
       <c r="Z20">
-        <v>21.28233420395572</v>
+        <v>1.650762658536451</v>
       </c>
       <c r="AA20">
-        <v>30.10120297939409</v>
+        <v>33.48138535230559</v>
       </c>
       <c r="AB20">
-        <v>47.03832662892981</v>
+        <v>52.08889368704357</v>
       </c>
       <c r="AC20">
-        <v>5.547652326601551E-17</v>
+        <v>-2.287904066007056E-15</v>
       </c>
       <c r="AF20">
-        <v>59.08592253709106</v>
+        <v>20.27729746292588</v>
       </c>
       <c r="AG20">
-        <v>6.700529722408637</v>
+        <v>9.326571642910727</v>
       </c>
       <c r="AH20">
-        <v>1140.063760504206</v>
+        <v>1273.463378525792</v>
       </c>
       <c r="AJ20">
-        <v>2267.057882519373</v>
+        <v>2640.199872326787</v>
       </c>
       <c r="AK20">
-        <v>725.6207506297584</v>
+        <v>852.9933709798016</v>
       </c>
       <c r="AL20">
-        <v>97.88332208190447</v>
+        <v>95.05639977349179</v>
       </c>
       <c r="AM20">
-        <v>84.0589746409885</v>
+        <v>36.9666722080155</v>
       </c>
       <c r="AN20">
-        <v>18.36305771991691</v>
+        <v>17.35898704408823</v>
       </c>
       <c r="AO20">
-        <v>104.0202181116369</v>
+        <v>126.7365967963998</v>
       </c>
       <c r="AP20">
-        <v>1599.825839296082</v>
+        <v>1855.915637757537</v>
       </c>
       <c r="AQ20">
-        <v>132.8290494358507</v>
+        <v>137.5848558477437</v>
       </c>
       <c r="AR20">
-        <v>120.5614431756327</v>
+        <v>149.4243403137135</v>
       </c>
       <c r="AS20">
-        <v>10.29030656002864</v>
+        <v>19.27028285513146</v>
       </c>
       <c r="AT20">
-        <v>252.8870358425381</v>
+        <v>346.5683223979797</v>
       </c>
       <c r="AU20">
-        <v>146.0506576587825</v>
+        <v>125.017250061003</v>
       </c>
       <c r="AV20">
         <v>1</v>
@@ -3103,121 +3094,124 @@
         </is>
       </c>
       <c r="B21">
-        <v>452.7240028518658</v>
+        <v>500.5072090164188</v>
       </c>
       <c r="C21">
-        <v>116.5670456782979</v>
+        <v>128.6956731574676</v>
       </c>
       <c r="D21">
-        <v>6861.477492561828</v>
+        <v>7647.460346518154</v>
       </c>
       <c r="E21">
-        <v>157.6782216178646</v>
+        <v>256.0864878336683</v>
       </c>
       <c r="F21">
-        <v>421.6398123060395</v>
+        <v>465.6112090849708</v>
       </c>
       <c r="G21">
-        <v>31.10746579054506</v>
+        <v>33.44146850679735</v>
       </c>
       <c r="H21">
-        <v>16.79631817464102</v>
+        <v>14.410378667866</v>
       </c>
       <c r="I21">
-        <v>236.9611850885213</v>
+        <v>299.400520753681</v>
       </c>
       <c r="J21">
-        <v>45.92689230087066</v>
+        <v>47.80989887551495</v>
       </c>
       <c r="K21">
-        <v>0.01883763050581912</v>
+        <v>0.01663475607408144</v>
       </c>
       <c r="L21">
-        <v>4714.528626296023</v>
+        <v>5213.480465318383</v>
       </c>
       <c r="M21">
-        <v>1039.409070412854</v>
+        <v>1154.212862208707</v>
       </c>
       <c r="N21">
-        <v>1107.539795852951</v>
+        <v>1279.767018991064</v>
       </c>
       <c r="O21">
-        <v>92.24402043324702</v>
+        <v>143.5376147383556</v>
       </c>
       <c r="P21">
-        <v>83.44566340080303</v>
+        <v>81.34825472138691</v>
       </c>
       <c r="S21">
-        <v>53.69559906021281</v>
+        <v>98.33743100543192</v>
       </c>
       <c r="T21">
-        <v>33.47738593489544</v>
+        <v>41.27404319521645</v>
       </c>
       <c r="U21">
-        <v>14.65264551263353</v>
+        <v>18.07326421222965</v>
       </c>
       <c r="V21">
-        <v>220.7552378829243</v>
+        <v>214.1170469978149</v>
       </c>
       <c r="W21">
-        <v>156.6304802138754</v>
+        <v>193.3140053239869</v>
       </c>
       <c r="Z21">
-        <v>2.160607214159966</v>
+        <v>1.969230145855138</v>
       </c>
       <c r="AA21">
-        <v>21.15482688618605</v>
+        <v>28.18029245501756</v>
       </c>
       <c r="AB21">
-        <v>15.87910735918107</v>
+        <v>10.29929337210614</v>
       </c>
       <c r="AC21">
-        <v>2.078582241831485E-16</v>
+        <v>-3.104504613083753E-15</v>
+      </c>
+      <c r="AE21">
+        <v>0.1388024948024948</v>
       </c>
       <c r="AF21">
-        <v>36.9586064440677</v>
+        <v>45.27443290979114</v>
       </c>
       <c r="AG21">
-        <v>2.63511013182093</v>
+        <v>0.9851897585593121</v>
       </c>
       <c r="AH21">
-        <v>3211.484502195472</v>
+        <v>3554.063257155585</v>
       </c>
       <c r="AJ21">
-        <v>235.6594434410919</v>
+        <v>272.7224276812456</v>
       </c>
       <c r="AK21">
-        <v>803.3178926210495</v>
+        <v>871.4183460577714</v>
       </c>
       <c r="AL21">
-        <v>139.0230558368126</v>
+        <v>138.1542413120389</v>
       </c>
       <c r="AM21">
-        <v>203.7967974825052</v>
+        <v>239.2922010501954</v>
       </c>
       <c r="AN21">
-        <v>50.66131631448775</v>
+        <v>47.80878818349469</v>
       </c>
       <c r="AO21">
-        <v>88.39437032258955</v>
+        <v>100.6878483582833</v>
       </c>
       <c r="AP21">
-        <v>883.536458522809</v>
+        <v>1007.426772310656</v>
       </c>
       <c r="AQ21">
-        <v>41.21409093211459</v>
+        <v>39.89381486465182</v>
       </c>
       <c r="AR21">
-        <v>34.74086258343891</v>
+        <v>36.76146096662185</v>
       </c>
       <c r="AS21">
-        <v>3.472378131880759</v>
+        <v>5.538892657980997</v>
       </c>
       <c r="AT21">
-        <v>50.90797356279349</v>
+        <v>52.42502053469339</v>
       </c>
       <c r="AU21">
-        <v>62.31476651224715</v>
+        <v>63.18444512394216</v>
       </c>
       <c r="AV21">
         <v>1</v>
@@ -3230,124 +3224,127 @@
         </is>
       </c>
       <c r="B22">
-        <v>654.4236350071167</v>
+        <v>735.3055150006805</v>
       </c>
       <c r="C22">
-        <v>170.6628518797059</v>
+        <v>170.0816171519465</v>
       </c>
       <c r="D22">
-        <v>6199.746019279012</v>
+        <v>7074.101274406649</v>
       </c>
       <c r="E22">
-        <v>474.7278068444827</v>
+        <v>702.3866317830813</v>
       </c>
       <c r="F22">
-        <v>565.4024571130765</v>
+        <v>636.1082541038918</v>
       </c>
       <c r="G22">
-        <v>87.35177222786412</v>
+        <v>97.24737017016193</v>
       </c>
       <c r="H22">
-        <v>21.70227366028887</v>
+        <v>20.27886355691953</v>
       </c>
       <c r="I22">
-        <v>199.8487311536709</v>
+        <v>199.3410962151297</v>
       </c>
       <c r="J22">
-        <v>55.79300854136184</v>
+        <v>54.9112007990169</v>
       </c>
       <c r="K22">
-        <v>0.02283210273457037</v>
+        <v>3.643809541906234</v>
       </c>
       <c r="L22">
-        <v>2753.912867486845</v>
+        <v>3118.696785660024</v>
       </c>
       <c r="M22">
-        <v>2448.113551904918</v>
+        <v>2826.519117362694</v>
       </c>
       <c r="N22">
-        <v>997.7195998872493</v>
+        <v>1128.885371383932</v>
       </c>
       <c r="O22">
-        <v>372.6121021613991</v>
+        <v>616.2235557677528</v>
       </c>
       <c r="P22">
-        <v>53.47757141276175</v>
+        <v>56.70726118342905</v>
       </c>
       <c r="Q22">
-        <v>0.02751221529950105</v>
+        <v>0.008253024506255816</v>
       </c>
       <c r="S22">
-        <v>64.06382671217044</v>
+        <v>51.26614119043931</v>
       </c>
       <c r="T22">
-        <v>83.19793666343828</v>
+        <v>90.11703068245085</v>
       </c>
       <c r="U22">
-        <v>73.573535990463</v>
+        <v>78.94122161162456</v>
       </c>
       <c r="V22">
-        <v>192.6918256654515</v>
+        <v>205.7243870562696</v>
       </c>
       <c r="W22">
-        <v>215.8762462990608</v>
+        <v>261.1749940655035</v>
       </c>
       <c r="Z22">
-        <v>0.08178624306182554</v>
+        <v>0.2237793079500502</v>
       </c>
       <c r="AA22">
-        <v>31.57054394820379</v>
+        <v>39.04091865516931</v>
       </c>
       <c r="AB22">
-        <v>58.01247741084675</v>
+        <v>64.39862720807693</v>
       </c>
       <c r="AC22">
-        <v>-4.163700954427681E-15</v>
+        <v>-6.780048395757842E-16</v>
       </c>
       <c r="AD22">
-        <v>2.462730908152735</v>
+        <v>2.404985727444346</v>
       </c>
       <c r="AF22">
-        <v>28.11545457766758</v>
+        <v>32.99515529504266</v>
+      </c>
+      <c r="AG22">
+        <v>0.003866172025281671</v>
       </c>
       <c r="AH22">
-        <v>1822.490368291183</v>
+        <v>2020.530226206849</v>
       </c>
       <c r="AJ22">
-        <v>60.18740174195143</v>
+        <v>70.72421068193752</v>
       </c>
       <c r="AK22">
-        <v>617.8939406409702</v>
+        <v>727.4089620270735</v>
       </c>
       <c r="AL22">
-        <v>87.10740325954656</v>
+        <v>97.20628525213442</v>
       </c>
       <c r="AM22">
-        <v>18.12880586005885</v>
+        <v>33.45768866685519</v>
       </c>
       <c r="AN22">
-        <v>29.35983297235399</v>
+        <v>29.53502989482972</v>
       </c>
       <c r="AO22">
-        <v>128.4574615226735</v>
+        <v>142.9005968878484</v>
       </c>
       <c r="AP22">
-        <v>1925.581304027521</v>
+        <v>2220.108124250088</v>
       </c>
       <c r="AQ22">
-        <v>148.9763692251304</v>
+        <v>155.8752219650086</v>
       </c>
       <c r="AR22">
-        <v>52.71833514395464</v>
+        <v>101.3360090896537</v>
       </c>
       <c r="AS22">
-        <v>14.20248987497398</v>
+        <v>15.85880390133695</v>
       </c>
       <c r="AT22">
-        <v>9.710327707637118</v>
+        <v>8.307309736927188</v>
       </c>
       <c r="AU22">
-        <v>354.0513284849845</v>
+        <v>344.1304223055339</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3360,115 +3357,115 @@
         </is>
       </c>
       <c r="B23">
-        <v>433.0138019214096</v>
+        <v>446.0969372552447</v>
       </c>
       <c r="C23">
-        <v>49.53740741721771</v>
+        <v>55.02805657459191</v>
       </c>
       <c r="D23">
-        <v>4920.527279381608</v>
+        <v>5529.019267295256</v>
       </c>
       <c r="E23">
-        <v>153.0179512794123</v>
+        <v>210.6185484945813</v>
       </c>
       <c r="F23">
-        <v>413.3163482393508</v>
+        <v>425.5109191870501</v>
       </c>
       <c r="G23">
-        <v>14.06408752877063</v>
+        <v>12.97163407599636</v>
       </c>
       <c r="H23">
-        <v>26.2890420486782</v>
+        <v>35.5337919635917</v>
       </c>
       <c r="I23">
-        <v>121.07005478881</v>
+        <v>130.7338973216033</v>
       </c>
       <c r="J23">
-        <v>36.08517910734994</v>
+        <v>41.95466684243158</v>
       </c>
       <c r="K23">
-        <v>-1.584660110922632E-14</v>
+        <v>-1.534692806646624E-14</v>
       </c>
       <c r="L23">
-        <v>1916.845776062677</v>
+        <v>2376.981280868997</v>
       </c>
       <c r="M23">
-        <v>1481.863196977311</v>
+        <v>1414.60821062782</v>
       </c>
       <c r="N23">
-        <v>1521.81830634162</v>
+        <v>1737.429775798439</v>
       </c>
       <c r="O23">
-        <v>130.0541205223338</v>
+        <v>187.8273661519494</v>
       </c>
       <c r="P23">
-        <v>3.734349412322025</v>
+        <v>5.311899241145852</v>
       </c>
       <c r="S23">
-        <v>22.43035226960398</v>
+        <v>21.65291821952906</v>
       </c>
       <c r="T23">
-        <v>29.09711257887</v>
+        <v>28.22869560084434</v>
       </c>
       <c r="U23">
-        <v>28.87336074367468</v>
+        <v>28.2061757746862</v>
       </c>
       <c r="V23">
-        <v>270.4962484457524</v>
+        <v>271.906414406621</v>
       </c>
       <c r="W23">
-        <v>98.56819699465147</v>
+        <v>111.2807640872981</v>
       </c>
       <c r="Z23">
-        <v>1.036004444229681</v>
+        <v>-5.404360319086195E-15</v>
       </c>
       <c r="AA23">
-        <v>7.829697274573173</v>
+        <v>8.022424370274603</v>
       </c>
       <c r="AB23">
-        <v>9.697940395418268</v>
+        <v>6.298994170918602</v>
       </c>
       <c r="AC23">
-        <v>-2.502229946892449E-16</v>
+        <v>-9.026492016135392E-16</v>
       </c>
       <c r="AF23">
-        <v>26.2890420486782</v>
+        <v>35.5337919635917</v>
       </c>
       <c r="AH23">
-        <v>774.9806894188067</v>
+        <v>827.3215843223403</v>
       </c>
       <c r="AJ23">
-        <v>14.26726673817149</v>
+        <v>14.86381783488562</v>
       </c>
       <c r="AK23">
-        <v>615.8264761103867</v>
+        <v>927.2558737556816</v>
       </c>
       <c r="AL23">
-        <v>136.0672978231339</v>
+        <v>148.4808812787591</v>
       </c>
       <c r="AM23">
-        <v>80.10534249469279</v>
+        <v>158.2912504035421</v>
       </c>
       <c r="AN23">
-        <v>30.0563864830564</v>
+        <v>44.89798885487215</v>
       </c>
       <c r="AO23">
-        <v>288.4295577071984</v>
+        <v>267.1764023048837</v>
       </c>
       <c r="AP23">
-        <v>1006.162140498387</v>
+        <v>994.9714693350694</v>
       </c>
       <c r="AQ23">
-        <v>23.34376878057172</v>
+        <v>24.82363208729171</v>
       </c>
       <c r="AR23">
-        <v>63.4649598878441</v>
+        <v>36.27266159715779</v>
       </c>
       <c r="AS23">
-        <v>17.64521051338247</v>
+        <v>3.814679993240846</v>
       </c>
       <c r="AU23">
-        <v>395.4380062925743</v>
+        <v>357.9954933235524</v>
       </c>
       <c r="AV23">
         <v>1</v>
@@ -3481,133 +3478,133 @@
         </is>
       </c>
       <c r="B24">
-        <v>905.7586300082619</v>
+        <v>1031.579334734526</v>
       </c>
       <c r="C24">
-        <v>233.7201683373287</v>
+        <v>251.5318090091402</v>
       </c>
       <c r="D24">
-        <v>8565.447660972377</v>
+        <v>9101.414872766622</v>
       </c>
       <c r="E24">
-        <v>769.6903183139372</v>
+        <v>1082.15616296099</v>
       </c>
       <c r="F24">
-        <v>814.8021478866739</v>
+        <v>926.6947367746608</v>
       </c>
       <c r="G24">
-        <v>82.99883250819796</v>
+        <v>95.94402483147759</v>
       </c>
       <c r="H24">
-        <v>16.41647098422955</v>
+        <v>18.52819946791845</v>
       </c>
       <c r="I24">
-        <v>260.7027381966376</v>
+        <v>278.5506593136229</v>
       </c>
       <c r="J24">
-        <v>51.03076319491475</v>
+        <v>56.12057283233984</v>
       </c>
       <c r="K24">
-        <v>1.630706784159956</v>
+        <v>1.860689247480703</v>
       </c>
       <c r="L24">
-        <v>4953.686942799995</v>
+        <v>5328.720622915509</v>
       </c>
       <c r="M24">
-        <v>2650.337800729849</v>
+        <v>2692.227802941826</v>
       </c>
       <c r="N24">
-        <v>971.4303658118278</v>
+        <v>1080.466446909286</v>
       </c>
       <c r="O24">
-        <v>557.177274040362</v>
+        <v>874.7413454978166</v>
       </c>
       <c r="P24">
-        <v>100.996325025534</v>
+        <v>114.0752077109033</v>
       </c>
       <c r="Q24">
-        <v>11.76888628919247</v>
+        <v>14.93492419072816</v>
       </c>
       <c r="R24">
-        <v>6.163480293324412</v>
+        <v>4.435880155336733</v>
       </c>
       <c r="S24">
-        <v>116.1115651693904</v>
+        <v>96.246302035764</v>
       </c>
       <c r="T24">
-        <v>198.1008445807955</v>
+        <v>220.6051723471401</v>
       </c>
       <c r="U24">
-        <v>101.9260645762921</v>
+        <v>118.6791181789837</v>
       </c>
       <c r="V24">
-        <v>252.0461280262462</v>
+        <v>286.59643872676</v>
       </c>
       <c r="W24">
-        <v>259.7701260681309</v>
+        <v>295.660349998362</v>
       </c>
       <c r="Z24">
-        <v>10.53987609074026</v>
+        <v>11.53075280218674</v>
       </c>
       <c r="AA24">
-        <v>26.80805825384487</v>
+        <v>28.4164441912733</v>
       </c>
       <c r="AB24">
-        <v>57.92342496094086</v>
+        <v>68.5624820014032</v>
       </c>
       <c r="AC24">
-        <v>3.584251757136752E-16</v>
+        <v>1.19115358809284E-15</v>
       </c>
       <c r="AD24">
-        <v>16.64368758375687</v>
+        <v>19.03907345416913</v>
       </c>
       <c r="AE24">
-        <v>0.6196369921600312</v>
+        <v>1.135602582452303</v>
       </c>
       <c r="AF24">
-        <v>21.00461359098939</v>
+        <v>20.30093759831261</v>
       </c>
       <c r="AG24">
-        <v>3.81870875912075</v>
+        <v>4.509747861230466</v>
       </c>
       <c r="AH24">
-        <v>3988.065207784174</v>
+        <v>4435.733093377401</v>
       </c>
       <c r="AJ24">
-        <v>137.9524579922108</v>
+        <v>122.6520830422104</v>
       </c>
       <c r="AK24">
-        <v>455.8720917917372</v>
+        <v>488.4039853057215</v>
       </c>
       <c r="AL24">
-        <v>98.1339696985512</v>
+        <v>94.83243992128801</v>
       </c>
       <c r="AM24">
-        <v>23.9998891798681</v>
+        <v>33.7382465974739</v>
       </c>
       <c r="AN24">
-        <v>39.46608516406034</v>
+        <v>42.38932308482197</v>
       </c>
       <c r="AO24">
-        <v>225.3028727731942</v>
+        <v>117.7642929183138</v>
       </c>
       <c r="AP24">
-        <v>2032.895625933782</v>
+        <v>2082.635292275251</v>
       </c>
       <c r="AQ24">
-        <v>241.0679452547562</v>
+        <v>241.9699458424987</v>
       </c>
       <c r="AR24">
-        <v>115.9107122119657</v>
+        <v>145.5905592201943</v>
       </c>
       <c r="AS24">
-        <v>8.567141567157497</v>
+        <v>15.34762460134454</v>
       </c>
       <c r="AT24">
-        <v>65.39834612468293</v>
+        <v>36.61616008435637</v>
       </c>
       <c r="AU24">
-        <v>264.3670687970849</v>
+        <v>218.7589938193743</v>
       </c>
       <c r="AV24">
         <v>1</v>
@@ -3620,133 +3617,133 @@
         </is>
       </c>
       <c r="B25">
-        <v>1048.061146987578</v>
+        <v>1185.975139882347</v>
       </c>
       <c r="C25">
-        <v>155.8871947821793</v>
+        <v>165.3536995975672</v>
       </c>
       <c r="D25">
-        <v>7483.124362966222</v>
+        <v>8052.512660768194</v>
       </c>
       <c r="E25">
-        <v>479.2849286659094</v>
+        <v>628.2266148979086</v>
       </c>
       <c r="F25">
-        <v>910.7236983759599</v>
+        <v>1031.684811423651</v>
       </c>
       <c r="G25">
-        <v>130.9947809868992</v>
+        <v>149.667359376649</v>
       </c>
       <c r="H25">
-        <v>14.14902777821948</v>
+        <v>11.24922476631554</v>
       </c>
       <c r="I25">
-        <v>244.4719832466407</v>
+        <v>284.5425322954725</v>
       </c>
       <c r="J25">
-        <v>82.80204378919467</v>
+        <v>87.78141138391265</v>
       </c>
       <c r="K25">
-        <v>1.990705109470722</v>
+        <v>0.03262569226268733</v>
       </c>
       <c r="L25">
-        <v>3589.357335534311</v>
+        <v>3946.699950051145</v>
       </c>
       <c r="M25">
-        <v>2868.359196266761</v>
+        <v>2997.846412343469</v>
       </c>
       <c r="N25">
-        <v>1025.40783116515</v>
+        <v>1107.96629837358</v>
       </c>
       <c r="O25">
-        <v>279.7613310657559</v>
+        <v>423.7902834347027</v>
       </c>
       <c r="P25">
-        <v>122.0958117585587</v>
+        <v>132.3860006694533</v>
       </c>
       <c r="Q25">
-        <v>11.74128742520352</v>
+        <v>13.81041950298377</v>
       </c>
       <c r="R25">
-        <v>24.28150985680288</v>
+        <v>18.52253699785579</v>
       </c>
       <c r="S25">
-        <v>87.6747706421145</v>
+        <v>83.5141908031876</v>
       </c>
       <c r="T25">
-        <v>184.2400409932156</v>
+        <v>203.2261135273958</v>
       </c>
       <c r="U25">
-        <v>125.6428198038524</v>
+        <v>142.430404408459</v>
       </c>
       <c r="V25">
-        <v>341.1613033161262</v>
+        <v>377.7177322923181</v>
       </c>
       <c r="W25">
-        <v>258.7764222119027</v>
+        <v>306.1574459287075</v>
       </c>
       <c r="Z25">
-        <v>5.573813165242743</v>
+        <v>4.838593222063728</v>
       </c>
       <c r="AA25">
-        <v>56.69753035831229</v>
+        <v>61.84616857746305</v>
       </c>
       <c r="AB25">
-        <v>76.13499181021277</v>
+        <v>89.35117670161077</v>
       </c>
       <c r="AC25">
-        <v>-4.178386954109185E-16</v>
+        <v>5.56169388497354E-16</v>
       </c>
       <c r="AD25">
-        <v>9.347770219812075</v>
+        <v>8.503216065243363</v>
       </c>
       <c r="AE25">
-        <v>6.678916727758837</v>
+        <v>12.76759375756741</v>
       </c>
       <c r="AF25">
-        <v>44.78439300303318</v>
+        <v>35.50623038910868</v>
       </c>
       <c r="AG25">
-        <v>1.822461077719692</v>
+        <v>6.250202025130831</v>
       </c>
       <c r="AH25">
-        <v>2804.058626111417</v>
+        <v>3076.223155479389</v>
       </c>
       <c r="AJ25">
-        <v>135.4304487349217</v>
+        <v>134.4843852240486</v>
       </c>
       <c r="AK25">
-        <v>417.6018474085</v>
+        <v>470.5815193102653</v>
       </c>
       <c r="AL25">
-        <v>106.6180757505262</v>
+        <v>100.815466367737</v>
       </c>
       <c r="AM25">
-        <v>32.89134983326667</v>
+        <v>43.83680646404046</v>
       </c>
       <c r="AN25">
-        <v>24.65706271070316</v>
+        <v>25.8769836765678</v>
       </c>
       <c r="AO25">
-        <v>88.56378204236276</v>
+        <v>101.0958001823152</v>
       </c>
       <c r="AP25">
-        <v>2340.516397625434</v>
+        <v>2446.704979485154</v>
       </c>
       <c r="AQ25">
-        <v>231.3492716766316</v>
+        <v>251.0161228042938</v>
       </c>
       <c r="AR25">
-        <v>57.83076608287913</v>
+        <v>64.49406439242074</v>
       </c>
       <c r="AS25">
-        <v>22.5561828933184</v>
+        <v>23.45149507581805</v>
       </c>
       <c r="AT25">
-        <v>178.3351933524442</v>
+        <v>100.4752440462378</v>
       </c>
       <c r="AU25">
-        <v>217.9268664397202</v>
+        <v>212.1841155378953</v>
       </c>
       <c r="AV25">
         <v>1</v>
@@ -3759,109 +3756,112 @@
         </is>
       </c>
       <c r="B26">
-        <v>502.0739395949411</v>
+        <v>577.3188132844346</v>
       </c>
       <c r="C26">
-        <v>71.04527479334713</v>
+        <v>88.14702852617467</v>
       </c>
       <c r="D26">
-        <v>6133.264149503444</v>
+        <v>7113.26603101855</v>
       </c>
       <c r="E26">
-        <v>631.1878051891555</v>
+        <v>385.3474828674426</v>
       </c>
       <c r="F26">
-        <v>484.9475957720422</v>
+        <v>557.7185458722008</v>
       </c>
       <c r="G26">
-        <v>17.59555872215645</v>
+        <v>20.13726103996622</v>
       </c>
       <c r="I26">
-        <v>99.13319940758893</v>
+        <v>126.372225252207</v>
       </c>
       <c r="J26">
-        <v>66.00460363702905</v>
+        <v>79.86032523094798</v>
+      </c>
+      <c r="K26">
+        <v>2.332340582741219E-14</v>
       </c>
       <c r="L26">
-        <v>3770.063366774201</v>
+        <v>4476.461555895289</v>
       </c>
       <c r="M26">
-        <v>997.7163808473613</v>
+        <v>1093.309552596021</v>
       </c>
       <c r="N26">
-        <v>1365.484401881881</v>
+        <v>1543.49492252724</v>
       </c>
       <c r="O26">
-        <v>525.8794408700992</v>
+        <v>296.022913317131</v>
       </c>
       <c r="P26">
-        <v>45.76502251562754</v>
+        <v>40.69313806186648</v>
       </c>
       <c r="S26">
-        <v>97.98596071655592</v>
+        <v>83.93277107474282</v>
       </c>
       <c r="T26">
-        <v>32.46455589856698</v>
+        <v>36.71028401459969</v>
       </c>
       <c r="U26">
-        <v>19.06481433158032</v>
+        <v>20.20783419021303</v>
       </c>
       <c r="V26">
-        <v>156.8805668878137</v>
+        <v>183.2291352160234</v>
       </c>
       <c r="W26">
-        <v>279.9729500027577</v>
+        <v>320.875419008015</v>
       </c>
       <c r="Z26">
-        <v>-1.107700156253453E-14</v>
+        <v>0.001646866527650801</v>
       </c>
       <c r="AA26">
-        <v>17.03240603805681</v>
+        <v>20.09661716447586</v>
       </c>
       <c r="AB26">
-        <v>10.27753648481854</v>
+        <v>0.7417507276990836</v>
       </c>
       <c r="AC26">
-        <v>-1.211592206615723E-15</v>
+        <v>-3.121282116366065E-16</v>
       </c>
       <c r="AH26">
-        <v>2424.44753931174</v>
+        <v>2697.554534351786</v>
       </c>
       <c r="AJ26">
-        <v>283.8419052715647</v>
+        <v>385.8018807020262</v>
       </c>
       <c r="AK26">
-        <v>632.8522829967271</v>
+        <v>836.3816616652213</v>
       </c>
       <c r="AL26">
-        <v>136.5400761734014</v>
+        <v>138.6378263141017</v>
       </c>
       <c r="AM26">
-        <v>165.1381044770739</v>
+        <v>243.2103401344479</v>
       </c>
       <c r="AN26">
-        <v>39.16375801508147</v>
+        <v>38.73688524788579</v>
       </c>
       <c r="AO26">
-        <v>116.7036386379728</v>
+        <v>139.381232014946</v>
       </c>
       <c r="AP26">
-        <v>807.5287516595517</v>
+        <v>868.7809839172901</v>
       </c>
       <c r="AQ26">
-        <v>57.84500830168745</v>
+        <v>64.98120325029976</v>
       </c>
       <c r="AR26">
-        <v>26.68872587472963</v>
+        <v>28.20229969968051</v>
       </c>
       <c r="AS26">
-        <v>30.59262659122433</v>
+        <v>44.89052409084466</v>
       </c>
       <c r="AT26">
-        <v>7.495071203400093</v>
+        <v>10.01578593106039</v>
       </c>
       <c r="AU26">
-        <v>80.02528061045712</v>
+        <v>89.27280970010362</v>
       </c>
       <c r="AV26">
         <v>1</v>
@@ -3874,133 +3874,133 @@
         </is>
       </c>
       <c r="B27">
-        <v>1129.406364607003</v>
+        <v>1244.898524040178</v>
       </c>
       <c r="C27">
-        <v>171.5422361115393</v>
+        <v>181.0698426290762</v>
       </c>
       <c r="D27">
-        <v>6693.318366529751</v>
+        <v>7319.693410738366</v>
       </c>
       <c r="E27">
-        <v>439.6467121212226</v>
+        <v>466.6588257423832</v>
       </c>
       <c r="F27">
-        <v>1038.223520600973</v>
+        <v>1146.277901053154</v>
       </c>
       <c r="G27">
-        <v>87.0444073569483</v>
+        <v>94.87679437346125</v>
       </c>
       <c r="H27">
-        <v>12.19617719475495</v>
+        <v>11.45817579663863</v>
       </c>
       <c r="I27">
-        <v>231.1772535812032</v>
+        <v>246.3608178040394</v>
       </c>
       <c r="J27">
-        <v>64.55765289544689</v>
+        <v>67.35573116882203</v>
       </c>
       <c r="K27">
-        <v>4.291310660911844</v>
+        <v>3.598857806089743</v>
       </c>
       <c r="L27">
-        <v>3481.436899005564</v>
+        <v>3805.078020734939</v>
       </c>
       <c r="M27">
-        <v>2359.255616151879</v>
+        <v>2616.739727527851</v>
       </c>
       <c r="N27">
-        <v>856.6100843226466</v>
+        <v>903.513814202267</v>
       </c>
       <c r="O27">
-        <v>208.2743284343089</v>
+        <v>221.0422506187614</v>
       </c>
       <c r="P27">
-        <v>173.2885827443294</v>
+        <v>175.0872837220563</v>
       </c>
       <c r="Q27">
-        <v>2.85586827038898</v>
+        <v>4.344172116676698</v>
       </c>
       <c r="R27">
-        <v>2.000253338291389</v>
+        <v>1.181639278571671</v>
       </c>
       <c r="S27">
-        <v>98.8446331435041</v>
+        <v>111.677181273829</v>
       </c>
       <c r="T27">
-        <v>299.3566736298747</v>
+        <v>328.659353635851</v>
       </c>
       <c r="U27">
-        <v>121.6041056783243</v>
+        <v>130.6201284162451</v>
       </c>
       <c r="V27">
-        <v>400.7275862798555</v>
+        <v>433.3149149886308</v>
       </c>
       <c r="W27">
-        <v>214.1728872159327</v>
+        <v>250.3859969833492</v>
       </c>
       <c r="Z27">
-        <v>4.168458705176964</v>
+        <v>6.897887561756233</v>
       </c>
       <c r="AA27">
-        <v>33.80165089763454</v>
+        <v>36.84390563785018</v>
       </c>
       <c r="AB27">
-        <v>60.12100498511062</v>
+        <v>64.63179203119371</v>
       </c>
       <c r="AC27">
-        <v>5.178818361290028E-16</v>
+        <v>1.940878656104455E-15</v>
       </c>
       <c r="AD27">
-        <v>1.361136310989476</v>
+        <v>1.665238684124251</v>
       </c>
       <c r="AE27">
-        <v>9.952927616602414</v>
+        <v>6.722916150199974</v>
       </c>
       <c r="AF27">
-        <v>40.37215005581126</v>
+        <v>38.82408039984279</v>
       </c>
       <c r="AG27">
-        <v>4.069602669542342</v>
+        <v>3.106879656265534</v>
       </c>
       <c r="AH27">
-        <v>2699.980103667373</v>
+        <v>2998.851743120937</v>
       </c>
       <c r="AJ27">
-        <v>148.8623160209644</v>
+        <v>142.7605467522664</v>
       </c>
       <c r="AK27">
-        <v>410.0764463618369</v>
+        <v>439.8035641949485</v>
       </c>
       <c r="AL27">
-        <v>104.8418583188296</v>
+        <v>95.20716810786905</v>
       </c>
       <c r="AM27">
-        <v>16.15440374655985</v>
+        <v>23.95661283019205</v>
       </c>
       <c r="AN27">
-        <v>24.60817337797004</v>
+        <v>25.68708160030294</v>
       </c>
       <c r="AO27">
-        <v>93.00015696182527</v>
+        <v>95.8134588256803</v>
       </c>
       <c r="AP27">
-        <v>1788.048253947492</v>
+        <v>1973.872967156138</v>
       </c>
       <c r="AQ27">
-        <v>254.7602906075047</v>
+        <v>276.5120476183987</v>
       </c>
       <c r="AR27">
-        <v>123.7692720189739</v>
+        <v>155.8442723102716</v>
       </c>
       <c r="AS27">
-        <v>12.91977855274076</v>
+        <v>21.22963937358354</v>
       </c>
       <c r="AT27">
-        <v>13.10898993050712</v>
+        <v>12.39953680262162</v>
       </c>
       <c r="AU27">
-        <v>201.4438471813099</v>
+        <v>216.4061125885461</v>
       </c>
       <c r="AV27">
         <v>1</v>
@@ -4013,124 +4013,127 @@
         </is>
       </c>
       <c r="B28">
-        <v>-511.4394682508866</v>
+        <v>574.5826298785489</v>
       </c>
       <c r="C28">
-        <v>148.630579000153</v>
+        <v>111.4465119473491</v>
       </c>
       <c r="D28">
-        <v>8947.297161174647</v>
+        <v>8944.189999122507</v>
       </c>
       <c r="E28">
-        <v>451.3162177596303</v>
+        <v>222.3298463493575</v>
       </c>
       <c r="F28">
-        <v>-535.6041903169684</v>
+        <v>549.8190856395711</v>
       </c>
       <c r="G28">
-        <v>22.75119276577823</v>
+        <v>23.18032951096759</v>
       </c>
       <c r="H28">
-        <v>16.5080335368125</v>
+        <v>19.4148161937559</v>
       </c>
       <c r="I28">
-        <v>268.8375860867253</v>
+        <v>189.4619670744927</v>
       </c>
       <c r="J28">
-        <v>34.12053838475831</v>
+        <v>36.99272281013427</v>
       </c>
       <c r="K28">
-        <v>11.02052715239326</v>
+        <v>5.938240872175045E-16</v>
       </c>
       <c r="L28">
-        <v>5456.677587376748</v>
+        <v>5410.532540475614</v>
       </c>
       <c r="M28">
-        <v>1801.42776996478</v>
+        <v>2024.349385696395</v>
       </c>
       <c r="N28">
-        <v>1689.19180383312</v>
+        <v>1509.3080729505</v>
       </c>
       <c r="O28">
-        <v>154.6210336015978</v>
+        <v>176.7440237823293</v>
       </c>
       <c r="P28">
-        <v>869.5240510166891</v>
+        <v>121.9699687481536</v>
       </c>
       <c r="Q28">
-        <v>6.467406085245154</v>
+        <v>12.98147891380372</v>
       </c>
       <c r="S28">
-        <v>44.12865444359382</v>
+        <v>16.64739873202118</v>
       </c>
       <c r="T28">
-        <v>-1169.287672330013</v>
+        <v>31.09801125573763</v>
       </c>
       <c r="U28">
-        <v>205.7578865466492</v>
+        <v>138.720797826301</v>
       </c>
       <c r="V28">
-        <v>255.9370750119042</v>
+        <v>240.9143864976693</v>
       </c>
       <c r="W28">
-        <v>114.1943742660675</v>
+        <v>142.622316941001</v>
       </c>
       <c r="Z28">
-        <v>0.9915649518195944</v>
+        <v>1.43865203555422</v>
       </c>
       <c r="AA28">
-        <v>9.256948403016919</v>
+        <v>11.68583297042613</v>
       </c>
       <c r="AB28">
-        <v>15.71069280634384</v>
+        <v>13.40846870199749</v>
       </c>
       <c r="AC28">
-        <v>-4.996122769839588E-16</v>
+        <v>-1.877822842173898E-16</v>
+      </c>
+      <c r="AD28">
+        <v>0.0008327328758771298</v>
       </c>
       <c r="AF28">
-        <v>21.33334832177167</v>
+        <v>21.76116461561307</v>
       </c>
       <c r="AG28">
-        <v>4.499113461635229</v>
+        <v>9.90045019597234</v>
       </c>
       <c r="AH28">
-        <v>3784.633319370402</v>
+        <v>3744.676932244915</v>
       </c>
       <c r="AJ28">
-        <v>198.9105140854401</v>
+        <v>117.8920314325084</v>
       </c>
       <c r="AK28">
-        <v>896.0609301631742</v>
+        <v>1038.05974743105</v>
       </c>
       <c r="AL28">
-        <v>153.2910802375869</v>
+        <v>133.7038538435976</v>
       </c>
       <c r="AM28">
-        <v>71.29806690822879</v>
+        <v>100.8427847720346</v>
       </c>
       <c r="AN28">
-        <v>80.08751437874281</v>
+        <v>56.59246246868586</v>
       </c>
       <c r="AO28">
-        <v>355.5495302786446</v>
+        <v>222.8640284768074</v>
       </c>
       <c r="AP28">
-        <v>1372.134207962068</v>
+        <v>1470.967783569237</v>
       </c>
       <c r="AQ28">
-        <v>93.98995903261986</v>
+        <v>96.58857595687546</v>
       </c>
       <c r="AR28">
-        <v>45.27571277736986</v>
+        <v>49.70543151065699</v>
       </c>
       <c r="AS28">
-        <v>9.96046254641157</v>
+        <v>8.822803441543471</v>
       </c>
       <c r="AT28">
-        <v>74.72072089981546</v>
+        <v>46.91916992302737</v>
       </c>
       <c r="AU28">
-        <v>332.010621085307</v>
+        <v>410.4816819067848</v>
       </c>
       <c r="AV28">
         <v>1</v>
